--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>MEI</t>
   </si>
@@ -656,405 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44044</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43953</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43862</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43764</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43673</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43582</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43491</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43400</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43309</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43218</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43127</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>259500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>288000</v>
+      </c>
+      <c r="F8" s="3">
         <v>289700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>301200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>280100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>315900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>282400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>288700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>291600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>295500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>287800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>301000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>295300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>300800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>190900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>210600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>285900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>257200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>270200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>266000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>246900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>264000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>223400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>249000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>228000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>230100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>201200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>219800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>195600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>235500</v>
+      </c>
+      <c r="F9" s="3">
         <v>235100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>237500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>215200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>241800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>220600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>233700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>221300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>226300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>216100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>225600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>222300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>217300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>143900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>151400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>206600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>188600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>194400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>195400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>179600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>190600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>163300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>187100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>167900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>167300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>145600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>164500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>142200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>52500</v>
+      </c>
+      <c r="F10" s="3">
         <v>54600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>63700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>64900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>74100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>61800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>55000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>70300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>69200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>71700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>75400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>73000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>83500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>47000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>59200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>79300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>68600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>75800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>70600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>67300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>73400</v>
-      </c>
-      <c r="X10" s="3">
-        <v>60100</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>61900</v>
       </c>
       <c r="Z10" s="3">
         <v>60100</v>
       </c>
       <c r="AA10" s="3">
+        <v>61900</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>60100</v>
+      </c>
+      <c r="AC10" s="3">
         <v>62800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>55600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>55300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>53400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1112,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1203,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,55 +1298,61 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>57100</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H14" s="3">
         <v>-300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-2600</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-2100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-1900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-2300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1320,52 +1360,58 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>3800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>10900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>4200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>2600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F15" s="3">
         <v>5700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4700</v>
       </c>
       <c r="G15" s="3">
         <v>4700</v>
@@ -1377,10 +1423,10 @@
         <v>4700</v>
       </c>
       <c r="J15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="K15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="L15" s="3">
         <v>4800</v>
@@ -1392,16 +1438,16 @@
         <v>4800</v>
       </c>
       <c r="O15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="P15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Q15" s="3">
         <v>5000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>4700</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="R15" s="3">
-        <v>4800</v>
       </c>
       <c r="S15" s="3">
         <v>4700</v>
@@ -1410,40 +1456,46 @@
         <v>4800</v>
       </c>
       <c r="U15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="V15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="W15" s="3">
         <v>5000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>5500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>3700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>1900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>2000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>600</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1524,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>262500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>339300</v>
+      </c>
+      <c r="F17" s="3">
         <v>285900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>291000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>252500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>282900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>256500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>271200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>258700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>260200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>251800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>265100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>257200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>252500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>174200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>174300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>244400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>226500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>231600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>233000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>220900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>244900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>194700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>221400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>192400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>200400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>175800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>193800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>166500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="F18" s="3">
         <v>3800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>10200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>27600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>33000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>25900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>17500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>32900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>35300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>36000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>35900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>38100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>48300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>16700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>36300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>41500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>30700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>38600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>33000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>26000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>19100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>28700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>27600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>35600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>29700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>25400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>26000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>29100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,254 +1749,268 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>4900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>3200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>3500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>1900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="F21" s="3">
         <v>17800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>21900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>36100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>46100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>38200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>30800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>47900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>47400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>48500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>50800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>51300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>60200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>29300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>54500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>58700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>43600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>50300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>42800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>39900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>27600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>36600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>38900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>46200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>36400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>30400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>34600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>36200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F22" s="3">
         <v>2800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>2100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>2700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>2900</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1950,186 +2030,204 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>7800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>23000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>33400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>25900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>17200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>33500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>33000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>34800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>36600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>36500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>46200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>40100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>44000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>29000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>35600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>30100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>27700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>17600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>28200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>30800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>39100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>29100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>24800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>27900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>30300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>5800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>4100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>5500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5700</v>
       </c>
       <c r="M24" s="3">
         <v>5500</v>
       </c>
       <c r="N24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="O24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="P24" s="3">
         <v>4600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>10000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>5200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>7300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>7500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>4500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>6600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>4900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>4300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>4700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>6600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2315,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>8100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>19900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>27600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>21500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>16200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>29400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>27500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>29100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>31100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>31900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>38600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>20700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>30100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>41200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>23800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>28300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>22600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>25900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>14600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>23700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>33700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>32500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>24200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>20500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>23200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>23700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>8100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>27600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>21500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>29400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>27500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>29100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>31100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>31900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>38600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>20700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>30100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>41200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>23800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>28300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>22600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>25900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>14600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>23700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>33700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>32500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>24200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>20500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>23200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>23700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2600,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2525,11 +2647,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2540,29 +2662,29 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>4800</v>
       </c>
-      <c r="W29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>3100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-56800</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2573,8 +2695,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2790,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +2885,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-5900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-4900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>8100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>27600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>21500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>16200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>29400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>27500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>29100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>31100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>31900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>38600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>20700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>30100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>41200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>23800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>28300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>22600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>30700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>14600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>23700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>36800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>24200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>20500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>23200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>23700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3170,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>8100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>27600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>21500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>16200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>29400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>27500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>29100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>31100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>31900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>38600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>20700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>30100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>41200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>23800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>28300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>22600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>30700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>14600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>23700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>36800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>24200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>20500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>23200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>23700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44044</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43953</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43862</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43764</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43673</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43582</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43491</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43400</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43309</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43218</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43127</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3404,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3439,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>122500</v>
+      </c>
+      <c r="F41" s="3">
         <v>147900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>157000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>164700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>129600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>152400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>172000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>153100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>177200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>207900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>233200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>218700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>242300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>211000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>217300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>79900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>95600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>73800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>83200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>73700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>110900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>228500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>246100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>304000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>258600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>297900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>294000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>268800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>249600</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,364 +3625,394 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>309000</v>
+      </c>
+      <c r="F43" s="3">
         <v>314200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>327200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>303000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>321000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>289700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>281600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>299400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>295000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>290000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>294000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>284000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>301100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>246600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>201400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>237600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>217300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>246500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>233600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>226200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>240200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>191000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>205000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>202000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>216000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>165100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>165900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>153800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>183900</v>
+      </c>
+      <c r="F44" s="3">
         <v>175600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>159700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>175400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>172500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>173900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>158500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>167000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>149000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>142400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>124200</v>
-      </c>
-      <c r="N44" s="3">
-        <v>124000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>120700</v>
       </c>
       <c r="P44" s="3">
         <v>124000</v>
       </c>
       <c r="Q44" s="3">
+        <v>120700</v>
+      </c>
+      <c r="R44" s="3">
+        <v>124000</v>
+      </c>
+      <c r="S44" s="3">
         <v>131000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>126100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>133800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>122000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>116700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>124000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>118300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>88500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>84100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>83600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>78400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>64800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>57900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>62000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F45" s="3">
         <v>19800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>20500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>27900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>35300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>23100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>16900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>20900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>21900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>20600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>22600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>18300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>18200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>16400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>15900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>20300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>18700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>19000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>20000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>22500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>21700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>15900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>14800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>15700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>15900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>19100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>12500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>14500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>629800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>636500</v>
+      </c>
+      <c r="F46" s="3">
         <v>657500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>664400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>671000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>658400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>639100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>629000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>640400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>643100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>660900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>674000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>645000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>682300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>598000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>565600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>463900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>465400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>461300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>453500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>446400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>491100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>523900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>550000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>605300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>568900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>546900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>530300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>499100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,186 +4100,204 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>251500</v>
+      </c>
+      <c r="F48" s="3">
         <v>254700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>248700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>230100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>213800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>212800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>217000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>218600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>228400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>235200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>226300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>228700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>226700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>230700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>225400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>226300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>226700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>222500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>191900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>189100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>187900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>165300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>162200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>153700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>126900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>117400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>90600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>87700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>484700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>485400</v>
+      </c>
+      <c r="F49" s="3">
         <v>553800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>558600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>425800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>427700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>435300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>440700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>447300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>454100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>459300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>465000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>468500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>470300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>475400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>476400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>484200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>489400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>493400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>498200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>504400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>509000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>117000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>120200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>125200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>123400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>36100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4385,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4480,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>118600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>111500</v>
+      </c>
+      <c r="F52" s="3">
         <v>108100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>107400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>101600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>94400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>102700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>102400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>105000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>105100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>103600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>101700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>102300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>110000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>114100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>103200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>107900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>101200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>91700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>88100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>86300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>82500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>86600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>83500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>75600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>79100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>83000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>74900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>71400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4670,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1491500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1484900</v>
+      </c>
+      <c r="F54" s="3">
         <v>1574100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1579100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1428500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1394300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1389900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1389100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1411300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1430700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1459000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1467000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1444500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1489300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1418200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1370600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1282300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1282700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1268900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1231700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1226200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1270500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>892800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>915900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>959800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>898300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>783400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>704000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>667000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4804,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,135 +4839,143 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>133500</v>
+      </c>
+      <c r="F57" s="3">
         <v>131900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>138700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>113100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>124500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>116400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>108500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>115900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>118600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>110800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>122900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>117800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>112400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>83200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>73800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>88800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>97100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>90700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>91900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>88600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>105600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>79000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>89500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>87900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>99300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>81200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>75300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>67700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>13000</v>
       </c>
       <c r="I58" s="3">
         <v>13000</v>
       </c>
       <c r="J58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L58" s="3">
         <v>13200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>14700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>14800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>14900</v>
-      </c>
-      <c r="N58" s="3">
-        <v>15400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>15300</v>
       </c>
       <c r="P58" s="3">
         <v>15400</v>
@@ -4716,405 +4984,435 @@
         <v>15300</v>
       </c>
       <c r="R58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="S58" s="3">
+        <v>15300</v>
+      </c>
+      <c r="T58" s="3">
         <v>15100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>15200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>15400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>15700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>15200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>15300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3800</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>81800</v>
+      </c>
+      <c r="F59" s="3">
         <v>73300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>86100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>77300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>75500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>66400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>67100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>74600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>74500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>78500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>84900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>76000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>71000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>61400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>54700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>59700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>72000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>74700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>73300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>72600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>71300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>53900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>63100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>59500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>50700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>41500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>49100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>43500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>218300</v>
+      </c>
+      <c r="F60" s="3">
         <v>208400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>228000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>190900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>213000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>195800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>188600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>203700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>207800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>204100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>222700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>209200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>198700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>160000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>143800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>163600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>184300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>180800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>180900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>176400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>192200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>136800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>157000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>150300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>152300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>126500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>124400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>111200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>331100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>329000</v>
+      </c>
+      <c r="F61" s="3">
         <v>335800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>303600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>200800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>191000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>194200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>197500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>202400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>208400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>220600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>225200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>229200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>332300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>334400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>336800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>241900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>259900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>267700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>276900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>287700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>342300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>49200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>53400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>116000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>105500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>47600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>27000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>37000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>92700</v>
+      </c>
+      <c r="F62" s="3">
         <v>97600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>94600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>94200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>91500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>88500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>89200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>88800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>95000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>100000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>101100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>108500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>106900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>110000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>106600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>103900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>105900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>106100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>84200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>88000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>92700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>74600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>75500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>86300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>33700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>19900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>11500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>10900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5500,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5595,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5690,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>656500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>640000</v>
+      </c>
+      <c r="F66" s="3">
         <v>642700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>637300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>485900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>495500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>478500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>475300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>494900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>511200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>524700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>549000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>546900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>637900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>604400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>587200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>509400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>550100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>554600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>542000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>552100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>627200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>260600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>285900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>352600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>291500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>194000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>162900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>159100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5824,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5915,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +6010,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +6105,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6200,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>677600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>697000</v>
+      </c>
+      <c r="F72" s="3">
         <v>764800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>772700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>778200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>771200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>768100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>763900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>752900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>749800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>761900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>746000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>726600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>698900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>664600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>651900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>625600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>588500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>568900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>545200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>526700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>500000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>490000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>472000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>439200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>467400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>446600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>427000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>407200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>387200</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6390,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6485,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6580,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>844900</v>
+      </c>
+      <c r="F76" s="3">
         <v>931400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>941800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>942600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>898800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>911400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>913800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>916400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>919500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>934300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>918000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>897600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>851400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>813800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>783400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>772900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>732600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>714300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>689700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>674100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>643300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>632200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>630000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>607200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>606800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>589400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>541100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>507900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>492800</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6770,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44044</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43953</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43862</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43764</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43673</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43582</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43491</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43400</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43309</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43218</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43127</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>8100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>27600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>21500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>16200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>29400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>27500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>29100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>31100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>31900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>38600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>20700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>30100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>41200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>23800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>28300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>22600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>30700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>14600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>23700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>36800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>24200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>20500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>23200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>23700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +7004,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>12700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>12300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>12200</v>
       </c>
       <c r="H83" s="3">
         <v>12300</v>
       </c>
       <c r="I83" s="3">
+        <v>12200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K83" s="3">
         <v>13000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>13700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>13300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>12600</v>
       </c>
       <c r="M83" s="3">
         <v>13300</v>
       </c>
       <c r="N83" s="3">
+        <v>12600</v>
+      </c>
+      <c r="O83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="P83" s="3">
         <v>13500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>12600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>12100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>12300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>12300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>11900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>11800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>12700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>12200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>10000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>8400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>8100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>7100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>7300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>5600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>6700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>5900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +7190,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7285,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7380,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7475,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7570,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>49000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>55700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>15400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>12700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>42000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>20100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>27000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>9700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>36000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>87100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>40300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>16400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>58000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>14800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>48700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>19100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>37700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>28100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>16200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>20000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>30700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>41900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>21600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>23600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>38500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>43000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7704,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-13800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-11200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-12800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-9600</v>
       </c>
       <c r="I91" s="3">
         <v>-8400</v>
       </c>
       <c r="J91" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-15900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-10200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-8100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-13600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-13200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-12800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-8400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-10400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7890,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7985,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-13800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-125800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-12800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-9600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-8400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-8300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-5300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-15400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-10100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-8200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-13000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-13200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-12500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-8800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-431300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-29900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,19 +8119,21 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F96" s="3">
         <v>-5300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-5000</v>
       </c>
       <c r="G96" s="3">
         <v>-4900</v>
@@ -7674,76 +8142,82 @@
         <v>-5000</v>
       </c>
       <c r="I96" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J96" s="3">
         <v>-5000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-5100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-5100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-5200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-4200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-4100</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-5000</v>
       </c>
       <c r="Q96" s="3">
         <v>-4100</v>
       </c>
       <c r="R96" s="3">
-        <v>-4000</v>
+        <v>-5000</v>
       </c>
       <c r="S96" s="3">
         <v>-4100</v>
       </c>
       <c r="T96" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-4100</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-3600</v>
       </c>
       <c r="V96" s="3">
         <v>-4100</v>
       </c>
       <c r="W96" s="3">
-        <v>-4500</v>
+        <v>-3600</v>
       </c>
       <c r="X96" s="3">
         <v>-4100</v>
       </c>
       <c r="Y96" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-3400</v>
       </c>
       <c r="AC96" s="3">
         <v>-3400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8305,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8400,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,271 +8495,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F100" s="3">
         <v>12500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>66800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-14900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-27900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-20800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-10800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-34100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-51400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-18300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-15100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-108600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-6200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>91400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-23000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-12300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-14400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-14900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-58800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>300500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-70300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>6400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>56900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-18100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>2300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>7100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-3900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>16100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>15900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>4200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-7700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>35100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-22800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-19600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>18900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-24100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-30700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-25300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>14500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-23600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>31300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>137400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-15700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>21800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-9400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>9500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-37200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-117600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-57900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>45400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>3900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>25200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>19200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>MEI</t>
   </si>
@@ -656,431 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F7" s="2">
         <v>45318</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43862</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43764</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43673</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43582</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43491</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43400</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43309</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43218</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43127</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>258500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>277300</v>
+      </c>
+      <c r="F8" s="3">
         <v>259500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>288000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>289700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>301200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>280100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>315900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>282400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>288700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>291600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>295500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>287800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>301000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>295300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>300800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>190900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>210600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>285900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>257200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>270200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>266000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>246900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>264000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>223400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>249000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>228000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>230100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>201200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>219800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>195600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>213600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>241000</v>
+      </c>
+      <c r="F9" s="3">
         <v>222400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>235500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>235100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>237500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>215200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>241800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>220600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>233700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>221300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>226300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>216100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>225600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>222300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>217300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>143900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>151400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>206600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>188600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>194400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>195400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>179600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>190600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>163300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>187100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>167900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>167300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>145600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>164500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>142200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F10" s="3">
         <v>37100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>52500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>54600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>63700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>64900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>74100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>61800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>55000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>70300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>69200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>71700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>75400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>73000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>83500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>47000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>59200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>79300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>68600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>75800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>70600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>67300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>73400</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>60100</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>61900</v>
       </c>
       <c r="AB10" s="3">
         <v>60100</v>
       </c>
       <c r="AC10" s="3">
+        <v>61900</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>60100</v>
+      </c>
+      <c r="AE10" s="3">
         <v>62800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>55600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>55300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>53400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1114,8 +1139,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,8 +1236,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1304,61 +1337,67 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>51700</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>57100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>5500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-2600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-2100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-1900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-2300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1366,58 +1405,64 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>3800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>10900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>4200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>2600</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F15" s="3">
         <v>6100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>6200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>5700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4700</v>
       </c>
       <c r="I15" s="3">
         <v>4700</v>
@@ -1429,10 +1474,10 @@
         <v>4700</v>
       </c>
       <c r="L15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="M15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="N15" s="3">
         <v>4800</v>
@@ -1444,16 +1489,16 @@
         <v>4800</v>
       </c>
       <c r="Q15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="R15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="S15" s="3">
         <v>5000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>4700</v>
-      </c>
-      <c r="S15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="T15" s="3">
-        <v>4800</v>
       </c>
       <c r="U15" s="3">
         <v>4700</v>
@@ -1462,40 +1507,46 @@
         <v>4800</v>
       </c>
       <c r="W15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="X15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>5000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>5500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>3700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>2000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>1100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>600</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1526,198 +1577,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>338800</v>
+      </c>
+      <c r="F17" s="3">
         <v>262500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>339300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>285900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>291000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>252500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>282900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>256500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>271200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>258700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>260200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>251800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>265100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>257200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>252500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>174200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>174300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>244400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>226500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>231600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>233000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>220900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>244900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>194700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>221400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>192400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>200400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>175800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>193800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>166500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-61500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-51300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>10200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>27600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>33000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>25900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>17500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>32900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>35300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>36000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>35900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>38100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>48300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>16700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>36300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>41500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>30700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>38600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>33000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>26000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>19100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>28700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>27600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>35600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>29700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>25400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>26000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>29100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1751,272 +1816,286 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>5900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>3200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="F21" s="3">
         <v>9400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-36700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>17800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>21900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>36100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>46100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>38200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>30800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>47900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>47400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>48500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>50800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>51300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>60200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>29300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>54500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>58700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>43600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>50300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>42800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>39900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>27600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>36600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>38900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>46200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>36400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>30400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>34600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>36200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F22" s="3">
         <v>5000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>4400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>2100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>2400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>2700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>2900</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2036,198 +2115,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-55500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>7800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>23000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>33400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>25900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>17200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>33500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>33000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>34800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>36600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>36500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>46200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>15600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>40100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>44000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>29000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>35600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>30100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>27700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>17600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>28200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>30800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>39100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>29100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>24800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>27900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>30300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>4400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>5500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>5700</v>
       </c>
       <c r="O24" s="3">
         <v>5500</v>
       </c>
       <c r="P24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="R24" s="3">
         <v>4600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>7600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-5100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>10000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>7300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>7500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>4500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>6600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>4900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>4300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>6600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2321,198 +2418,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-11600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-55300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>8100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>19900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>27600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>21500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>16200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>29400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>27500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>29100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>31100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>31900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>38600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>20700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>30100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>41200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>23800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>28300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>22600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>25900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>14600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>23700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>33700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>32500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>24200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>20500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>23200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>23700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-11600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-55300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>8100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>19900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>27600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>21500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>16200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>29400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>27500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>29100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>31100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>31900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>38600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>20700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>30100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>41200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>23800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>28300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>22600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>25900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>14600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>23700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>33700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>32500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>24200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>20500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>23200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>23700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2606,8 +2721,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2653,11 +2774,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2668,29 +2789,29 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>4800</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>3100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>-56800</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2701,8 +2822,14 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2796,8 +2923,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2891,198 +3024,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F32" s="3">
         <v>2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-5900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-11600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-55300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>8100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>19900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>27600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>21500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>16200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>29400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>27500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>29100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>31100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>31900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>38600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>20700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>30100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>41200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>23800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>28300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>22600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>30700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>14600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>23700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>36800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>24200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>20500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>23200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>23700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3176,203 +3327,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-11600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-55300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>8100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>19900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>27600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>21500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>16200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>29400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>27500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>29100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>31100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>31900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>38600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>20700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>30100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>41200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>23800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>28300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>22600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>30700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>14600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>23700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>36800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>24200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>20500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>23200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>23700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F38" s="2">
         <v>45318</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43862</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43764</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43673</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43582</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43491</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43400</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43309</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43218</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43127</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3406,8 +3575,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3441,103 +3612,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>161500</v>
+      </c>
+      <c r="F41" s="3">
         <v>122900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>122500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>147900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>157000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>164700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>129600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>152400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>172000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>153100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>177200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>207900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>233200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>218700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>242300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>211000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>217300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>79900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>95600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>73800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>83200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>73700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>110900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>228500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>246100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>304000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>258600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>297900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>294000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>268800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>249600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3631,388 +3810,418 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>252700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>266600</v>
+      </c>
+      <c r="F43" s="3">
         <v>283900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>309000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>314200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>327200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>303000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>321000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>289700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>281600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>299400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>295000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>290000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>294000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>284000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>301100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>246600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>201400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>237600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>217300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>246500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>233600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>226200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>240200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>191000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>205000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>202000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>216000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>165100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>165900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>153800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>219900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>186200</v>
+      </c>
+      <c r="F44" s="3">
         <v>204000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>183900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>175600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>159700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>175400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>172500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>173900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>158500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>167000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>149000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>142400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>124200</v>
-      </c>
-      <c r="P44" s="3">
-        <v>124000</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>120700</v>
       </c>
       <c r="R44" s="3">
         <v>124000</v>
       </c>
       <c r="S44" s="3">
+        <v>120700</v>
+      </c>
+      <c r="T44" s="3">
+        <v>124000</v>
+      </c>
+      <c r="U44" s="3">
         <v>131000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>126100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>133800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>122000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>116700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>124000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>118300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>88500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>84100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>83600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>78400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>64800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>57900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>62000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="F45" s="3">
         <v>19000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>21100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>19800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>20500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>27900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>35300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>23100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>20900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>21900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>20600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>22600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>18300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>18200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>16400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>15900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>20300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>18700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>19000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>20000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>22500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>21700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>15900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>14800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>15700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>15900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>19100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>12500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>14500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>611800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>637700</v>
+      </c>
+      <c r="F46" s="3">
         <v>629800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>636500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>657500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>664400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>671000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>658400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>639100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>629000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>640400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>643100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>660900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>674000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>645000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>682300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>598000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>565600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>463900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>465400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>461300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>453500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>446400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>491100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>523900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>550000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>605300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>568900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>546900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>530300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>499100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4106,198 +4315,216 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>239200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>238800</v>
+      </c>
+      <c r="F48" s="3">
         <v>258400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>251500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>254700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>248700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>230100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>213800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>212800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>217000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>218600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>228400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>235200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>226300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>228700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>226700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>230700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>225400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>226300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>226700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>222500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>191900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>189100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>187900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>165300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>162200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>153700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>126900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>117400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>90600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>87700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>422800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>426600</v>
+      </c>
+      <c r="F49" s="3">
         <v>484700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>485400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>553800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>558600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>425800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>427700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>435300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>440700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>447300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>454100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>459300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>465000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>468500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>470300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>475400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>476400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>484200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>489400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>493400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>498200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>504400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>509000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>117000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>120200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>125200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>123400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>36100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>8800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4391,8 +4618,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4486,103 +4719,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>100400</v>
+      </c>
+      <c r="F52" s="3">
         <v>118600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>111500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>108100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>107400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>101600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>94400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>102700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>102400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>105000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>105100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>103600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>101700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>102300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>110000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>114100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>103200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>107900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>101200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>91700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>88100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>86300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>82500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>86600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>83500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>75600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>79100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>83000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>74900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>71400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4676,103 +4921,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1377900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1403500</v>
+      </c>
+      <c r="F54" s="3">
         <v>1491500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1484900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1574100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1579100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1428500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1394300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1389900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1389100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1411300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1430700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1459000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1467000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1444500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1489300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1418200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1370600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1282300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1282700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1268900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1231700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1226200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1270500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>892800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>915900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>959800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>898300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>783400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>704000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>667000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4806,8 +5063,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4841,103 +5100,111 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>161100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>132400</v>
+      </c>
+      <c r="F57" s="3">
         <v>146000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>133500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>131900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>138700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>113100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>124500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>116400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>108500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>115900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>118600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>110800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>122900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>117800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>112400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>83200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>73800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>88800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>97100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>90700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>91900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>88600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>105600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>79000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>89500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>87900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>99300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>81200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>75300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>67700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4945,43 +5212,43 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>13000</v>
       </c>
       <c r="K58" s="3">
         <v>13000</v>
       </c>
       <c r="L58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N58" s="3">
         <v>13200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>14700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>14800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>14900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>15400</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>15300</v>
       </c>
       <c r="R58" s="3">
         <v>15400</v>
@@ -4990,429 +5257,459 @@
         <v>15300</v>
       </c>
       <c r="T58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="U58" s="3">
+        <v>15300</v>
+      </c>
+      <c r="V58" s="3">
         <v>15100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>15200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>15400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>15700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>15200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>15300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>4400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3800</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F59" s="3">
         <v>83700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>81800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>73300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>86100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>77300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>75500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>66400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>67100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>74600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>74500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>78500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>84900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>76000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>71000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>61400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>54700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>59700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>72000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>74700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>73300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>72600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>71300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>53900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>63100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>59500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>50700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>41500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>49100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>43500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>260800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>231400</v>
+      </c>
+      <c r="F60" s="3">
         <v>229900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>218300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>208400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>228000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>190900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>213000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>195800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>188600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>203700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>207800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>204100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>222700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>209200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>198700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>160000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>143800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>163600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>184300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>180800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>180900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>176400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>192200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>136800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>157000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>150300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>152300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>126500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>124400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>111200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>295800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>331000</v>
+      </c>
+      <c r="F61" s="3">
         <v>331100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>329000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>335800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>303600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>200800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>191000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>194200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>197500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>202400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>208400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>220600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>225200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>229200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>332300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>334400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>336800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>241900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>259900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>267700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>276900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>287700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>342300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>49200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>53400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>116000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>105500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>47600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>27000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>37000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>75100</v>
+      </c>
+      <c r="F62" s="3">
         <v>95500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>92700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>97600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>94600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>94200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>91500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>88500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>89200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>88800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>95000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>100000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>101100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>108500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>106900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>110000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>106600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>103900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>105900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>106100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>84200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>88000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>92700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>74600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>75500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>86300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>33700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>19900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>11500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>10900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5506,8 +5803,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5601,8 +5904,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5696,103 +6005,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>633500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>637500</v>
+      </c>
+      <c r="F66" s="3">
         <v>656500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>640000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>642700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>637300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>485900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>495500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>478500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>475300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>494900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>511200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>524700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>549000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>546900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>637900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>604400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>587200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>509400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>550100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>554600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>542000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>552100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>627200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>260600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>285900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>352600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>291500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>194000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>162900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>159100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5826,8 +6147,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5921,8 +6244,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6016,8 +6345,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6111,8 +6446,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6206,103 +6547,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>587100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>612300</v>
+      </c>
+      <c r="F72" s="3">
         <v>677600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>697000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>764800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>772700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>778200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>771200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>768100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>763900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>752900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>749800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>761900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>746000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>726600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>698900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>664600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>651900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>625600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>588500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>568900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>545200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>526700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>500000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>490000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>472000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>439200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>467400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>446600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>427000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>407200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>387200</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6396,8 +6749,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6491,8 +6850,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6586,103 +6951,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>744400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>766000</v>
+      </c>
+      <c r="F76" s="3">
         <v>835000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>844900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>931400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>941800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>942600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>898800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>911400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>913800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>916400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>919500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>934300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>918000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>897600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>851400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>813800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>783400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>772900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>732600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>714300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>689700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>674100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>643300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>632200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>630000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>607200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>606800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>589400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>541100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>507900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>492800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6776,203 +7153,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F80" s="2">
         <v>45318</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43862</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43764</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43673</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43582</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43491</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43400</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43309</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43218</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43127</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-11600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-55300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>8100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>19900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>27600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>21500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>16200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>29400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>27500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>29100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>31100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>31900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>38600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>20700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>30100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>41200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>23800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>28300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>22600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>30700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>14600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>23700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>36800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>24200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>20500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>23200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>23700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7006,103 +7401,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F83" s="3">
         <v>14900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>14400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>14000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>12700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>12300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>12200</v>
       </c>
       <c r="J83" s="3">
         <v>12300</v>
       </c>
       <c r="K83" s="3">
+        <v>12200</v>
+      </c>
+      <c r="L83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="M83" s="3">
         <v>13000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>13700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>13300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>12600</v>
       </c>
       <c r="O83" s="3">
         <v>13300</v>
       </c>
       <c r="P83" s="3">
+        <v>12600</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="R83" s="3">
         <v>13500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>12600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>12100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>12300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>12300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>11900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>11800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>12700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>12200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>10000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>8400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>8100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>7100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>7300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>5600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>6700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>5900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7196,8 +7599,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7291,8 +7700,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7386,8 +7801,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7481,8 +7902,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7576,103 +8003,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F89" s="3">
         <v>28800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>49000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>55700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>15400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>12700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>42000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>20100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>27000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>9700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>36000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>87100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>40300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>16400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>58000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>14800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>48700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>19100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>37700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>28100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>16200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>20000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>30700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>41900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>21600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>23600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>38500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>43000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7706,103 +8145,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-16600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-10700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-13800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-11200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-12800</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-9600</v>
       </c>
       <c r="K91" s="3">
         <v>-8400</v>
       </c>
       <c r="L91" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-8300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-15900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-10200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-8100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-13600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-13200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-12800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7896,8 +8343,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7991,103 +8444,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-16700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-8500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-13800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-125800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-12800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-9600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-15400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-11600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-10100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-8200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-13000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-13200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-12500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-431300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-29900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8121,25 +8586,27 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-4900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="G96" s="3">
         <v>-4800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-5300</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-5000</v>
       </c>
       <c r="I96" s="3">
         <v>-4900</v>
@@ -8148,76 +8615,82 @@
         <v>-5000</v>
       </c>
       <c r="K96" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L96" s="3">
         <v>-5000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-5100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-5100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-5200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-4200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-4100</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-5000</v>
       </c>
       <c r="S96" s="3">
         <v>-4100</v>
       </c>
       <c r="T96" s="3">
-        <v>-4000</v>
+        <v>-5000</v>
       </c>
       <c r="U96" s="3">
         <v>-4100</v>
       </c>
       <c r="V96" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-4100</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-3600</v>
       </c>
       <c r="X96" s="3">
         <v>-4100</v>
       </c>
       <c r="Y96" s="3">
-        <v>-4500</v>
+        <v>-3600</v>
       </c>
       <c r="Z96" s="3">
         <v>-4100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-3400</v>
       </c>
       <c r="AE96" s="3">
         <v>-3400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8311,8 +8784,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8406,8 +8885,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8501,289 +8986,313 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-16900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-10600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>12500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>66800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-14900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-27900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-20800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-10800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-34100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-51400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-18300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-15100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-108600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-6200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-13000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>91400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-23000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-12300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-14400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-14900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-58800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>300500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-70300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>6400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>56900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-18100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F101" s="3">
         <v>5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>7100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-1900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>2300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>16100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>15900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>4200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-50200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>38600</v>
+      </c>
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-25400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-7700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>35100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-22800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-19600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>18900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-24100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-30700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-25300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>14500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>31300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-6300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>137400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-15700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>21800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-9400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>9500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-117600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-57900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>45400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>3900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>25200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>19200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>MEI</t>
   </si>
@@ -656,456 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E7" s="2">
         <v>45500</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45409</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45318</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43862</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43764</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43673</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43582</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43491</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43400</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43309</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43218</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43127</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>292600</v>
+      </c>
+      <c r="E8" s="3">
         <v>258500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>277300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>259500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>288000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>289700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>301200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>280100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>315900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>282400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>288700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>291600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>295500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>287800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>301000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>295300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>300800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>190900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>210600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>285900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>257200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>270200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>266000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>246900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>264000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>223400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>249000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>228000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>230100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>201200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>219800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>195600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>234600</v>
+      </c>
+      <c r="E9" s="3">
         <v>213600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>241000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>222400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>235500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>235100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>237500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>215200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>241800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>220600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>233700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>221300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>226300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>216100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>225600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>222300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>217300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>143900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>151400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>206600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>188600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>194400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>195400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>179600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>190600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>163300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>187100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>167900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>167300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>145600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>164500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>142200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E10" s="3">
         <v>44900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>36300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>63700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>64900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>61800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>55000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>70300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>69200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>71700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>75400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>73000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>83500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>47000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>59200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>79300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>68600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>75800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>70600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>67300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>73400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>60100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>61900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>60100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>62800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>55600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>55300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>53400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,8 +1154,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1166,8 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="F12" s="3">
+        <v>49100</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1164,8 +1178,8 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>35000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1242,8 +1256,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,64 +1360,67 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>51700</v>
+        <v>600</v>
       </c>
       <c r="F14" s="3">
+        <v>50300</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>57100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
-        <v>5500</v>
-      </c>
       <c r="J14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2600</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-2100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>500</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1411,41 +1431,44 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>4200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1453,19 +1476,19 @@
         <v>5900</v>
       </c>
       <c r="E15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F15" s="3">
         <v>6000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4700</v>
       </c>
       <c r="J15" s="3">
         <v>4700</v>
@@ -1480,7 +1503,7 @@
         <v>4700</v>
       </c>
       <c r="N15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="O15" s="3">
         <v>4800</v>
@@ -1495,49 +1518,49 @@
         <v>4800</v>
       </c>
       <c r="S15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="T15" s="3">
         <v>5000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>4700</v>
       </c>
       <c r="U15" s="3">
         <v>4700</v>
       </c>
       <c r="V15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="W15" s="3">
         <v>4800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3700</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>1900</v>
       </c>
       <c r="AC15" s="3">
         <v>1900</v>
       </c>
       <c r="AD15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE15" s="3">
         <v>2000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>600</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
@@ -1545,8 +1568,11 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1605,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>266000</v>
+        <v>283100</v>
       </c>
       <c r="E17" s="3">
-        <v>338800</v>
+        <v>265400</v>
       </c>
       <c r="F17" s="3">
-        <v>262500</v>
+        <v>286100</v>
       </c>
       <c r="G17" s="3">
-        <v>339300</v>
+        <v>262400</v>
       </c>
       <c r="H17" s="3">
-        <v>285900</v>
+        <v>282200</v>
       </c>
       <c r="I17" s="3">
-        <v>291000</v>
+        <v>285200</v>
       </c>
       <c r="J17" s="3">
+        <v>284100</v>
+      </c>
+      <c r="K17" s="3">
         <v>252500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>282900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>256500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>271200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>258700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>260200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>251800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>265100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>257200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>252500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>174200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>174300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>244400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>226500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>231600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>233000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>220900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>244900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>194700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>221400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>192400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>200400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>175800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>193800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>166500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7500</v>
+        <v>9500</v>
       </c>
       <c r="E18" s="3">
-        <v>-61500</v>
+        <v>-6900</v>
       </c>
       <c r="F18" s="3">
-        <v>-3000</v>
+        <v>-8800</v>
       </c>
       <c r="G18" s="3">
-        <v>-51300</v>
+        <v>-2900</v>
       </c>
       <c r="H18" s="3">
-        <v>3800</v>
+        <v>5800</v>
       </c>
       <c r="I18" s="3">
-        <v>10200</v>
+        <v>4500</v>
       </c>
       <c r="J18" s="3">
+        <v>17100</v>
+      </c>
+      <c r="K18" s="3">
         <v>27600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>35300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>48300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>41500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>38600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>33000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>27600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>35600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>29700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>25400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>26000</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>29100</v>
       </c>
       <c r="AI18" s="3">
         <v>29100</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>29100</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1818,278 +1851,285 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-800</v>
+        <v>7800</v>
       </c>
       <c r="E20" s="3">
-        <v>2900</v>
+        <v>-600</v>
       </c>
       <c r="F20" s="3">
-        <v>-2500</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="I20" s="3">
-        <v>-1000</v>
+        <v>-700</v>
       </c>
       <c r="J20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-3800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3500</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-600</v>
       </c>
       <c r="AF20" s="3">
         <v>-600</v>
       </c>
       <c r="AG20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AH20" s="3">
         <v>1900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5800</v>
+        <v>7600</v>
       </c>
       <c r="E21" s="3">
-        <v>-44000</v>
+        <v>-400</v>
       </c>
       <c r="F21" s="3">
-        <v>9400</v>
+        <v>-2700</v>
       </c>
       <c r="G21" s="3">
-        <v>-36700</v>
+        <v>700</v>
       </c>
       <c r="H21" s="3">
-        <v>17800</v>
+        <v>7800</v>
       </c>
       <c r="I21" s="3">
-        <v>21900</v>
+        <v>10900</v>
       </c>
       <c r="J21" s="3">
+        <v>18300</v>
+      </c>
+      <c r="K21" s="3">
         <v>36100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>30800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>48500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>50800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>51300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>60200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>29300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>54500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>58700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>50300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>39900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>36600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>46200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>36400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>30400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>34600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>36200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>4800</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2800</v>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1100</v>
       </c>
       <c r="P22" s="3">
         <v>1100</v>
       </c>
       <c r="Q22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
@@ -2097,8 +2137,8 @@
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2121,210 +2161,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-63100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>46200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>15600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>40100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>35600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>30100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>27700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>30800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>39100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>29100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>24800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>27900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>30300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E24" s="3">
         <v>5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2424,210 +2473,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-57300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-55300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>29100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>38600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>30100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>41200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>28300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>22600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>25900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>33700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>32500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>24200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>23200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-57300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-55300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>29100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>38600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>20700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>41200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>28300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>22600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>25900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>33700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>32500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>24200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>23200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2785,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2780,8 +2841,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2795,26 +2856,26 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>4800</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>3100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-56800</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2828,8 +2889,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +2993,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,210 +3097,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>800</v>
+        <v>-7800</v>
       </c>
       <c r="E32" s="3">
-        <v>-2900</v>
+        <v>600</v>
       </c>
       <c r="F32" s="3">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>-2500</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="I32" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="J32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K32" s="3">
         <v>3800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3500</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>600</v>
       </c>
       <c r="AF32" s="3">
         <v>600</v>
       </c>
       <c r="AG32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-57300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-55300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>29100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>38600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>20700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>30100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>41200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>23800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>28300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>22600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>30700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>36800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>24200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3409,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-57300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-55300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>29100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>38600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>20700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>30100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>41200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>23800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>28300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>22600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>30700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>36800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>24200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E38" s="2">
         <v>45500</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45409</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45318</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43862</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43764</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43673</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43582</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43491</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43400</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43309</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43218</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43127</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3662,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,109 +3700,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E41" s="3">
         <v>111300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>161500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>122900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>147900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>157000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>164700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>129600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>152400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>172000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>153100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>207900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>233200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>218700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>242300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>211000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>217300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>79900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>95600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>73800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>83200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>73700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>110900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>228500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>246100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>304000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>258600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>297900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>294000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>268800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>249600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3736,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3816,435 +3906,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>260800</v>
+      </c>
+      <c r="E43" s="3">
         <v>252700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>266600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>283900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>309000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>314200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>327200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>303000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>321000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>289700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>281600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>299400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>295000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>290000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>294000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>284000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>301100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>246600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>201400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>237600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>217300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>246500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>233600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>226200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>240200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>191000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>205000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>202000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>216000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>165100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>165900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>153800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>228200</v>
+      </c>
+      <c r="E44" s="3">
         <v>219900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>186200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>204000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>183900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>175600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>159700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>175400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>172500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>173900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>158500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>167000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>149000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>142400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>124200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>124000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>120700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>124000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>131000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>126100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>133800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>122000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>116700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>124000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>118300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>88500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>84100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>83600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>78400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>64800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>57900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>62000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>27900</v>
       </c>
-      <c r="E45" s="3">
-        <v>23400</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="L45" s="3">
+        <v>35300</v>
+      </c>
+      <c r="M45" s="3">
+        <v>23100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>16900</v>
+      </c>
+      <c r="O45" s="3">
+        <v>20900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>21900</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>20600</v>
+      </c>
+      <c r="R45" s="3">
+        <v>22600</v>
+      </c>
+      <c r="S45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="T45" s="3">
+        <v>18200</v>
+      </c>
+      <c r="U45" s="3">
+        <v>16400</v>
+      </c>
+      <c r="V45" s="3">
+        <v>15900</v>
+      </c>
+      <c r="W45" s="3">
+        <v>20300</v>
+      </c>
+      <c r="X45" s="3">
+        <v>18700</v>
+      </c>
+      <c r="Y45" s="3">
         <v>19000</v>
       </c>
-      <c r="G45" s="3">
-        <v>21100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>19800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>20500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>27900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>35300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>23100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>16900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>20900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>21900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>20600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>22600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>18300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>18200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>16400</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="Z45" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>21700</v>
+      </c>
+      <c r="AC45" s="3">
         <v>15900</v>
       </c>
-      <c r="V45" s="3">
-        <v>20300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>18700</v>
-      </c>
-      <c r="X45" s="3">
-        <v>19000</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>22500</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>21700</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>15700</v>
+      </c>
+      <c r="AF45" s="3">
         <v>15900</v>
       </c>
-      <c r="AC45" s="3">
-        <v>14800</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>15700</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>15900</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>19100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>14500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>612900</v>
+      </c>
+      <c r="E46" s="3">
         <v>611800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>637700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>629800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>636500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>657500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>664400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>671000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>658400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>639100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>629000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>640400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>643100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>660900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>674000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>645000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>682300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>598000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>565600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>463900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>465400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>461300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>453500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>446400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>491100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>523900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>550000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>605300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>568900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>546900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>530300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>499100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4321,210 +4426,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>244400</v>
+      </c>
+      <c r="E48" s="3">
         <v>239200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>238800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>258400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>251500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>254700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>248700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>230100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>213800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>212800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>217000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>218600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>228400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>235200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>226300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>228700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>226700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>230700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>225400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>226300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>226700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>222500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>191900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>189100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>187900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>165300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>162200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>153700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>126900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>117400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>90600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>87700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>416400</v>
+      </c>
+      <c r="E49" s="3">
         <v>422800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>426600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>484700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>485400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>553800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>558600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>425800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>427700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>435300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>440700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>447300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>454100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>459300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>465000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>468500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>470300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>475400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>476400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>484200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>489400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>493400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>498200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>504400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>509000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>117000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>120200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>125200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>123400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>36100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4738,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,109 +4842,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>104100</v>
+        <v>21900</v>
       </c>
       <c r="E52" s="3">
-        <v>100400</v>
+        <v>22000</v>
       </c>
       <c r="F52" s="3">
-        <v>118600</v>
+        <v>21600</v>
       </c>
       <c r="G52" s="3">
-        <v>111500</v>
+        <v>34700</v>
       </c>
       <c r="H52" s="3">
-        <v>108100</v>
+        <v>34000</v>
       </c>
       <c r="I52" s="3">
-        <v>107400</v>
+        <v>35500</v>
       </c>
       <c r="J52" s="3">
+        <v>37700</v>
+      </c>
+      <c r="K52" s="3">
         <v>101600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>94400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>102700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>102400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>105000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>105100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>103600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>101700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>102300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>110000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>114100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>103200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>107900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>101200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>91700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>88100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>86300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>82500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>86600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>83500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>75600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>79100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>83000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>74900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>71400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,109 +5050,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1375100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1377900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1403500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1491500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1484900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1574100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1579100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1428500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1394300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1389900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1389100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1411300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1430700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1459000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1467000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1444500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1489300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1418200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1370600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1282300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1282700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1268900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1231700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1226200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1270500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>892800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>915900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>959800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>898300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>783400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>704000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>667000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5194,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,135 +5232,139 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E57" s="3">
         <v>161100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>132400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>146000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>133500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>131900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>138700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>113100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>124500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>116400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>108500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>115900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>118600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>110800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>122900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>117800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>112400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>83200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>73800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>88800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>97100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>90700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>91900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>88600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>105600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>79000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>89500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>87900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>99300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>81200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>75300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>67700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>7800</v>
       </c>
       <c r="E58" s="3">
-        <v>400</v>
+        <v>7100</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>6900</v>
       </c>
       <c r="G58" s="3">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="H58" s="3">
-        <v>3200</v>
+        <v>9600</v>
       </c>
       <c r="I58" s="3">
-        <v>3200</v>
+        <v>10100</v>
       </c>
       <c r="J58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>13000</v>
       </c>
       <c r="L58" s="3">
         <v>13000</v>
@@ -5239,64 +5373,64 @@
         <v>13000</v>
       </c>
       <c r="N58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O58" s="3">
         <v>13200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>15400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3800</v>
-      </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
@@ -5304,412 +5438,427 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>99500</v>
+        <v>8400</v>
       </c>
       <c r="E59" s="3">
-        <v>98600</v>
+        <v>9800</v>
       </c>
       <c r="F59" s="3">
-        <v>83700</v>
+        <v>8300</v>
       </c>
       <c r="G59" s="3">
-        <v>81800</v>
+        <v>7900</v>
       </c>
       <c r="H59" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K59" s="3">
+        <v>77300</v>
+      </c>
+      <c r="L59" s="3">
+        <v>75500</v>
+      </c>
+      <c r="M59" s="3">
+        <v>66400</v>
+      </c>
+      <c r="N59" s="3">
+        <v>67100</v>
+      </c>
+      <c r="O59" s="3">
+        <v>74600</v>
+      </c>
+      <c r="P59" s="3">
+        <v>74500</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>78500</v>
+      </c>
+      <c r="R59" s="3">
+        <v>84900</v>
+      </c>
+      <c r="S59" s="3">
+        <v>76000</v>
+      </c>
+      <c r="T59" s="3">
+        <v>71000</v>
+      </c>
+      <c r="U59" s="3">
+        <v>61400</v>
+      </c>
+      <c r="V59" s="3">
+        <v>54700</v>
+      </c>
+      <c r="W59" s="3">
+        <v>59700</v>
+      </c>
+      <c r="X59" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>74700</v>
+      </c>
+      <c r="Z59" s="3">
         <v>73300</v>
       </c>
-      <c r="I59" s="3">
-        <v>86100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>77300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>75500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>66400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>67100</v>
-      </c>
-      <c r="N59" s="3">
-        <v>74600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>74500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>78500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>84900</v>
-      </c>
-      <c r="R59" s="3">
-        <v>76000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>71000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>61400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>54700</v>
-      </c>
-      <c r="V59" s="3">
-        <v>59700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>72000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>74700</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>73300</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>71300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>53900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>63100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>59500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>50700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>41500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>49100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>43500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E60" s="3">
         <v>260800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>231400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>229900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>218300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>208400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>228000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>190900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>213000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>195800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>188600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>203700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>207800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>204100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>222700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>209200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>198700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>160000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>143800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>163600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>184300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>180800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>180900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>176400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>192200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>136800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>157000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>150300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>152300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>126500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>124400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>111200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>295800</v>
+        <v>366700</v>
       </c>
       <c r="E61" s="3">
-        <v>331000</v>
+        <v>319100</v>
       </c>
       <c r="F61" s="3">
-        <v>331100</v>
+        <v>353400</v>
       </c>
       <c r="G61" s="3">
-        <v>329000</v>
+        <v>355200</v>
       </c>
       <c r="H61" s="3">
-        <v>335800</v>
+        <v>351000</v>
       </c>
       <c r="I61" s="3">
-        <v>303600</v>
+        <v>359300</v>
       </c>
       <c r="J61" s="3">
+        <v>325400</v>
+      </c>
+      <c r="K61" s="3">
         <v>200800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>191000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>194200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>197500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>202400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>208400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>220600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>225200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>229200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>332300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>334400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>336800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>241900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>259900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>267700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>276900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>287700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>342300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>49200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>53400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>116000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>105500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>47600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>76900</v>
+        <v>16600</v>
       </c>
       <c r="E62" s="3">
-        <v>75100</v>
+        <v>25700</v>
       </c>
       <c r="F62" s="3">
-        <v>95500</v>
+        <v>24000</v>
       </c>
       <c r="G62" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>24700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>32700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K62" s="3">
+        <v>94200</v>
+      </c>
+      <c r="L62" s="3">
+        <v>91500</v>
+      </c>
+      <c r="M62" s="3">
+        <v>88500</v>
+      </c>
+      <c r="N62" s="3">
+        <v>89200</v>
+      </c>
+      <c r="O62" s="3">
+        <v>88800</v>
+      </c>
+      <c r="P62" s="3">
+        <v>95000</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>100000</v>
+      </c>
+      <c r="R62" s="3">
+        <v>101100</v>
+      </c>
+      <c r="S62" s="3">
+        <v>108500</v>
+      </c>
+      <c r="T62" s="3">
+        <v>106900</v>
+      </c>
+      <c r="U62" s="3">
+        <v>110000</v>
+      </c>
+      <c r="V62" s="3">
+        <v>106600</v>
+      </c>
+      <c r="W62" s="3">
+        <v>103900</v>
+      </c>
+      <c r="X62" s="3">
+        <v>105900</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>106100</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>84200</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>88000</v>
+      </c>
+      <c r="AB62" s="3">
         <v>92700</v>
       </c>
-      <c r="H62" s="3">
-        <v>97600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>94600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>94200</v>
-      </c>
-      <c r="K62" s="3">
-        <v>91500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>88500</v>
-      </c>
-      <c r="M62" s="3">
-        <v>89200</v>
-      </c>
-      <c r="N62" s="3">
-        <v>88800</v>
-      </c>
-      <c r="O62" s="3">
-        <v>95000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100000</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>101100</v>
-      </c>
-      <c r="R62" s="3">
-        <v>108500</v>
-      </c>
-      <c r="S62" s="3">
-        <v>106900</v>
-      </c>
-      <c r="T62" s="3">
-        <v>110000</v>
-      </c>
-      <c r="U62" s="3">
-        <v>106600</v>
-      </c>
-      <c r="V62" s="3">
-        <v>103900</v>
-      </c>
-      <c r="W62" s="3">
-        <v>105900</v>
-      </c>
-      <c r="X62" s="3">
-        <v>106100</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>84200</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>88000</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>92700</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>74600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>75500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>86300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>33700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +5958,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5910,8 +6062,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,109 +6166,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>636800</v>
+      </c>
+      <c r="E66" s="3">
         <v>633500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>637500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>656500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>640000</v>
       </c>
-      <c r="H66" s="3">
-        <v>642700</v>
-      </c>
       <c r="I66" s="3">
-        <v>637300</v>
+        <v>641800</v>
       </c>
       <c r="J66" s="3">
+        <v>626200</v>
+      </c>
+      <c r="K66" s="3">
         <v>485900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>495500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>478500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>475300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>494900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>511200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>524700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>549000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>546900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>637900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>604400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>587200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>509400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>550100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>554600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>542000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>552100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>627200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>260600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>285900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>352600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>291500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>194000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>162900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>159100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6310,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6412,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6516,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6620,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6724,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>580600</v>
+      </c>
+      <c r="E72" s="3">
         <v>587100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>612300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>677600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>697000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>764800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>772700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>778200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>771200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>768100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>763900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>752900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>749800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>761900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>746000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>726600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>698900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>664600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>651900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>625600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>588500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>568900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>545200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>526700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>500000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>490000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>472000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>439200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>467400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>446600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>427000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>407200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>387200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +6932,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7036,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7140,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>738300</v>
+      </c>
+      <c r="E76" s="3">
         <v>744400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>766000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>835000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>844900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>931400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>941800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>942600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>898800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>911400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>913800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>916400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>919500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>934300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>918000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>897600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>851400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>813800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>783400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>772900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>732600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>714300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>689700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>674100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>643300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>632200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>630000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>607200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>606800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>589400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>541100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>507900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>492800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7348,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E80" s="2">
         <v>45500</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45409</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45318</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43862</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43764</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43673</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43582</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43491</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43400</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43309</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43218</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43127</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-57300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-55300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>29100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>38600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>20700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>30100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>41200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>23800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>28300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>22600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>30700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>36800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>24200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,109 +7601,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14100</v>
+        <v>8200</v>
       </c>
       <c r="E83" s="3">
-        <v>14600</v>
+        <v>8300</v>
       </c>
       <c r="F83" s="3">
-        <v>14900</v>
+        <v>8000</v>
       </c>
       <c r="G83" s="3">
-        <v>14400</v>
+        <v>7600</v>
       </c>
       <c r="H83" s="3">
-        <v>14000</v>
+        <v>7500</v>
       </c>
       <c r="I83" s="3">
-        <v>12700</v>
+        <v>7600</v>
       </c>
       <c r="J83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K83" s="3">
         <v>12300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>12300</v>
       </c>
       <c r="V83" s="3">
         <v>12300</v>
       </c>
       <c r="W83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="X83" s="3">
         <v>11900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6700</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>5900</v>
       </c>
       <c r="AI83" s="3">
         <v>5900</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>5900</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +7807,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +7911,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8015,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8119,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,109 +8223,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E89" s="3">
         <v>10900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>49000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>55700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>36000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>87100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>40300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>58000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>19100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>16200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>20000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>30700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>41900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>21600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>23600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>38500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>43000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,109 +8367,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8573,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,109 +8677,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>21500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-125800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15400</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-4800</v>
       </c>
       <c r="R94" s="3">
         <v>-4800</v>
       </c>
       <c r="S94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="T94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-431300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-29900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,94 +8821,95 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5100</v>
+        <v>4900</v>
       </c>
       <c r="E96" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H96" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I96" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-4900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-5000</v>
       </c>
       <c r="M96" s="3">
         <v>-5000</v>
       </c>
       <c r="N96" s="3">
-        <v>-5100</v>
+        <v>-5000</v>
       </c>
       <c r="O96" s="3">
         <v>-5100</v>
       </c>
       <c r="P96" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4200</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-4100</v>
       </c>
       <c r="S96" s="3">
         <v>-4100</v>
       </c>
       <c r="T96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="U96" s="3">
         <v>-5000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-4100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-4100</v>
       </c>
       <c r="X96" s="3">
         <v>-4100</v>
       </c>
       <c r="Y96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-4500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-4100</v>
       </c>
       <c r="AC96" s="3">
         <v>-4100</v>
       </c>
       <c r="AD96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-3400</v>
       </c>
       <c r="AF96" s="3">
         <v>-3400</v>
@@ -8684,13 +8918,16 @@
         <v>-3400</v>
       </c>
       <c r="AH96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9027,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9131,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,307 +9235,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-48200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>66800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-51400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-108600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-13000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>91400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-23000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-58800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>300500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-70300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>6400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>56900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-18100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K101" s="3">
+        <v>7100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T101" s="3">
+        <v>800</v>
+      </c>
+      <c r="U101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F101" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="X101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AA101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
-        <v>7100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="R101" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S101" s="3">
-        <v>800</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="V101" s="3">
-        <v>700</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>2300</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>15900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4200</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-5600</v>
       </c>
       <c r="AI101" s="3">
         <v>-5600</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>-5600</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-50200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>38600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>35100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>137400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>21800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-117600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-57900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>45400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>25200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>19200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>MEI</t>
   </si>
@@ -656,469 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45598</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45409</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45318</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43862</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43764</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43673</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43582</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43491</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43400</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43309</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43218</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43127</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>239900</v>
+      </c>
+      <c r="E8" s="3">
         <v>292600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>258500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>277300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>259500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>288000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>289700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>301200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>280100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>315900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>282400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>288700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>291600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>295500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>287800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>301000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>295300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>300800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>190900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>210600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>285900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>257200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>270200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>266000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>246900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>264000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>223400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>249000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>228000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>230100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>201200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>219800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>195600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>198600</v>
+      </c>
+      <c r="E9" s="3">
         <v>234600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>213600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>241000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>222400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>235500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>235100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>237500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>215200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>241800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>220600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>233700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>221300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>226300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>216100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>225600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>222300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>217300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>143900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>151400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>206600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>188600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>194400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>195400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>179600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>190600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>163300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>187100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>167900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>167300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>145600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>164500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>142200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E10" s="3">
         <v>58000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>44900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>37100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>54600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>63700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>64900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>61800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>55000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>70300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>69200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>73000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>83500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>47000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>59200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>79300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>68600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>75800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>70600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>67300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>73400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>60100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>61900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>60100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>62800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>55600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>55300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>53400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1168,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,11 +1180,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>49100</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1178,11 +1192,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>35000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1259,8 +1273,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,67 +1380,70 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>50300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>57100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>500</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1434,64 +1454,67 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>4200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2600</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="E15" s="3">
         <v>5900</v>
       </c>
       <c r="F15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G15" s="3">
         <v>6000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4700</v>
       </c>
       <c r="K15" s="3">
         <v>4700</v>
@@ -1506,7 +1529,7 @@
         <v>4700</v>
       </c>
       <c r="O15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="P15" s="3">
         <v>4800</v>
@@ -1521,49 +1544,49 @@
         <v>4800</v>
       </c>
       <c r="T15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="U15" s="3">
         <v>5000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>4700</v>
       </c>
       <c r="V15" s="3">
         <v>4700</v>
       </c>
       <c r="W15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="X15" s="3">
         <v>4800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>1900</v>
       </c>
       <c r="AD15" s="3">
         <v>1900</v>
       </c>
       <c r="AE15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AF15" s="3">
         <v>2000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>600</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>8</v>
@@ -1571,8 +1594,11 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,216 +1632,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>242100</v>
+      </c>
+      <c r="E17" s="3">
         <v>283100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>265400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>286100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>262400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>282200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>285200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>284100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>252500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>282900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>256500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>271200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>258700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>260200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>251800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>265100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>257200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>252500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>174200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>174300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>244400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>226500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>231600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>233000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>220900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>244900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>194700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>221400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>192400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>200400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>175800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>193800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>166500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3">
         <v>9500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>35900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>48300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>36300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>41500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>30700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>38600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>33000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>28700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>27600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>35600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>29700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>25400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>26000</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>29100</v>
       </c>
       <c r="AJ18" s="3">
         <v>29100</v>
       </c>
+      <c r="AK18" s="3">
+        <v>29100</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1852,287 +1885,294 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>7800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3500</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-600</v>
       </c>
       <c r="AG20" s="3">
         <v>-600</v>
       </c>
       <c r="AH20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AI20" s="3">
         <v>1900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>30800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>50800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>51300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>60200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>29300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>54500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>58700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>43600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>50300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>27600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>36600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>46200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>36400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>30400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>34600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5000</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1100</v>
       </c>
       <c r="Q22" s="3">
         <v>1100</v>
       </c>
       <c r="R22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
@@ -2140,8 +2180,8 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2164,216 +2204,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-63100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-55500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>34800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>46200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>40100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>35600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>30100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>27700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>30800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>39100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>29100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>24800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>27900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2476,216 +2525,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-57300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-55300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>38600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>20700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>41200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>28300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>22600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>25900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>33700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>32500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>24200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-57300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-55300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>38600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>20700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>41200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>23800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>28300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>22600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>25900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>33700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>32500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>24200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2788,8 +2846,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2844,8 +2905,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2859,26 +2920,26 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>4800</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>3100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-56800</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2892,8 +2953,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2996,8 +3060,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,216 +3167,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3500</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>600</v>
       </c>
       <c r="AG32" s="3">
         <v>600</v>
       </c>
       <c r="AH32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-57300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-55300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>38600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>20700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>41200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>23800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>28300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>30700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>36800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>24200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3412,221 +3488,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-57300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-55300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>38600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>20700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>41200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>23800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>28300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>30700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>36800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>24200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45598</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45409</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45318</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43862</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43764</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43673</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43582</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43491</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43400</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43309</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43218</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43127</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,8 +3748,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,112 +3787,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E41" s="3">
         <v>97000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>161500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>147900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>157000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>164700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>152400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>172000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>153100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>207900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>233200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>218700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>242300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>211000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>217300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>95600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>73800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>83200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>73700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>110900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>228500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>246100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>304000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>258600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>297900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>294000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>268800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>249600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3826,14 +3916,14 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1600</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3909,424 +3999,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>224200</v>
+      </c>
+      <c r="E43" s="3">
         <v>260800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>252700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>266600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>283900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>309000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>314200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>327200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>303000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>321000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>289700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>281600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>299400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>295000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>290000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>294000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>284000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>301100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>246600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>201400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>237600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>217300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>246500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>233600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>226200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>240200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>191000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>205000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>202000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>216000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>165100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>165900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>153800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>218800</v>
+      </c>
+      <c r="E44" s="3">
         <v>228200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>219900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>186200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>204000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>183900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>175600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>159700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>175400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>172500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>173900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>158500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>167000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>149000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>142400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>124200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>124000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>120700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>124000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>131000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>126100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>133800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>122000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>116700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>124000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>118300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>88500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>84100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>83600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>78400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>64800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>57900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>62000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>18700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>22500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>21700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>15900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>15700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>15900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>19100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>572200</v>
+      </c>
+      <c r="E46" s="3">
         <v>612900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>611800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>637700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>629800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>636500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>657500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>664400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>671000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>658400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>639100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>629000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>640400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>643100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>660900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>674000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>645000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>682300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>598000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>565600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>463900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>465400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>461300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>453500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>446400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>491100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>523900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>550000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>605300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>568900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>546900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>530300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>499100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4351,8 +4456,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4429,216 +4534,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>233500</v>
+      </c>
+      <c r="E48" s="3">
         <v>244400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>239200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>238800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>258400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>251500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>254700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>248700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>230100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>213800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>212800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>217000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>218600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>228400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>235200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>226300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>228700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>226700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>230700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>225400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>226300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>226700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>222500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>191900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>189100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>187900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>165300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>162200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>153700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>126900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>117400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>90600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>87700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E49" s="3">
         <v>416400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>422800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>426600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>484700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>485400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>553800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>558600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>425800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>427700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>435300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>440700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>447300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>454100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>459300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>465000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>468500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>470300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>475400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>476400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>484200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>489400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>493400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>498200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>504400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>509000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>117000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>120200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>125200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>123400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>36100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4741,8 +4855,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4845,112 +4962,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E52" s="3">
         <v>21900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>34000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>37700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>101600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>94400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>102700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>102400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>105000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>105100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>103600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>101700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>102300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>110000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>114100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>103200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>107900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>101200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>91700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>88100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>86300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>82500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>86600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>83500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>75600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>79100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>83000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>74900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>71400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5053,112 +5176,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1304600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1375100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1377900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1403500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1491500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1484900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1574100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1579100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1428500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1394300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1389900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1389100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1411300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1430700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1459000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1467000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1444500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1489300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1418200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1370600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1282300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1282700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1268900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1231700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1226200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1270500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>892800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>915900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>959800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>898300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>783400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>704000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>667000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5195,8 +5324,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5233,141 +5363,145 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E57" s="3">
         <v>129800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>161100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>132400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>146000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>133500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>131900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>138700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>113100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>124500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>108500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>115900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>118600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>110800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>122900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>117800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>112400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>83200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>73800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>88800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>97100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>90700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>91900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>88600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>105600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>79000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>89500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>87900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>99300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>81200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>75300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>67700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>13000</v>
       </c>
       <c r="M58" s="3">
         <v>13000</v>
@@ -5376,64 +5510,64 @@
         <v>13000</v>
       </c>
       <c r="O58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P58" s="3">
         <v>13200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3800</v>
-      </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>8</v>
@@ -5441,424 +5575,439 @@
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E59" s="3">
         <v>8400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>75500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>66400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>78500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>76000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>61400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>54700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>59700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>72000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>74700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>73300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>72600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>71300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>53900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>63100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>59500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>50700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>41500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>49100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>43500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E60" s="3">
         <v>222600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>260800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>231400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>229900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>218300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>208400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>228000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>190900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>213000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>195800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>188600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>203700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>207800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>204100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>222700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>209200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>198700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>160000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>143800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>163600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>184300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>180800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>180900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>176400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>192200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>136800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>157000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>150300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>152300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>126500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>124400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>111200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>352200</v>
+      </c>
+      <c r="E61" s="3">
         <v>366700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>319100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>353400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>355200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>351000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>359300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>325400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>191000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>194200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>197500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>202400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>208400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>220600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>225200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>229200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>332300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>334400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>336800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>241900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>259900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>267700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>276900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>287700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>342300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>49200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>53400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>116000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>105500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>47600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E62" s="3">
         <v>16600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>94200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>91500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>88500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>89200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>88800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>95000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>100000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>101100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>108500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>106900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>110000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>106600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>103900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>105900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>106100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>84200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>88000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>92700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>74600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>75500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>86300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>33700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6110,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6065,8 +6217,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6169,112 +6324,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>600300</v>
+      </c>
+      <c r="E66" s="3">
         <v>636800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>633500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>637500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>656500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>640000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>641800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>626200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>485900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>495500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>478500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>475300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>494900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>511200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>524700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>549000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>546900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>637900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>604400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>587200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>509400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>550100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>554600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>542000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>552100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>627200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>260600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>285900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>352600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>291500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>194000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>162900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>159100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6311,8 +6472,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6415,8 +6577,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6519,8 +6684,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6623,8 +6791,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6727,112 +6898,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>558300</v>
+      </c>
+      <c r="E72" s="3">
         <v>580600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>587100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>612300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>677600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>697000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>764800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>772700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>778200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>771200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>768100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>763900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>752900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>749800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>761900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>746000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>726600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>698900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>664600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>651900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>625600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>588500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>568900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>545200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>526700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>500000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>490000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>472000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>439200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>467400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>446600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>427000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>407200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>387200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6935,8 +7112,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7039,8 +7219,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7143,112 +7326,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>704300</v>
+      </c>
+      <c r="E76" s="3">
         <v>738300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>744400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>766000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>835000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>844900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>931400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>941800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>942600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>898800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>911400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>913800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>916400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>919500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>934300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>918000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>897600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>851400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>813800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>783400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>772900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>732600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>714300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>689700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>674100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>643300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>632200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>630000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>607200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>606800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>589400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>541100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>507900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>492800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7351,221 +7540,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45598</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45409</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45318</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43862</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43764</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43673</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43582</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43491</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43400</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43309</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43218</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43127</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-57300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-55300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>38600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>20700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>41200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>23800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>28300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>30700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>36800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>24200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7602,112 +7800,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E83" s="3">
         <v>8200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12100</v>
-      </c>
-      <c r="V83" s="3">
-        <v>12300</v>
       </c>
       <c r="W83" s="3">
         <v>12300</v>
       </c>
       <c r="X83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>11900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6700</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>5900</v>
       </c>
       <c r="AJ83" s="3">
         <v>5900</v>
       </c>
+      <c r="AK83" s="3">
+        <v>5900</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7810,8 +8012,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7914,8 +8119,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8018,8 +8226,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8122,8 +8333,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8226,112 +8440,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-48000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>49000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>55700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>42000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>36000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>87100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>16400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>58000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>48700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>19100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>28100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>16200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>20000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>30700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>41900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>21600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>23600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>38500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8368,112 +8588,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8576,8 +8800,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8680,112 +8907,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>21500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-125800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15400</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-4800</v>
       </c>
       <c r="S94" s="3">
         <v>-4800</v>
       </c>
       <c r="T94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-431300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-29900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8822,97 +9055,98 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E96" s="3">
         <v>4900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5100</v>
-      </c>
-      <c r="F96" s="3">
-        <v>4900</v>
       </c>
       <c r="G96" s="3">
         <v>4900</v>
       </c>
       <c r="H96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I96" s="3">
         <v>4800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-5000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-4900</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-5000</v>
       </c>
       <c r="N96" s="3">
         <v>-5000</v>
       </c>
       <c r="O96" s="3">
-        <v>-5100</v>
+        <v>-5000</v>
       </c>
       <c r="P96" s="3">
         <v>-5100</v>
       </c>
       <c r="Q96" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="R96" s="3">
         <v>-5200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-4200</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-4100</v>
       </c>
       <c r="T96" s="3">
         <v>-4100</v>
       </c>
       <c r="U96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-4100</v>
       </c>
       <c r="Y96" s="3">
         <v>-4100</v>
       </c>
       <c r="Z96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-4500</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-4100</v>
       </c>
       <c r="AD96" s="3">
         <v>-4100</v>
       </c>
       <c r="AE96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-3400</v>
       </c>
       <c r="AG96" s="3">
         <v>-3400</v>
@@ -8921,13 +9155,16 @@
         <v>-3400</v>
       </c>
       <c r="AI96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9030,8 +9267,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9134,8 +9374,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9238,316 +9481,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E100" s="3">
         <v>40100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>66800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-108600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-13000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>91400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-58800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>300500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-70300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>6400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>56900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-18100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>15900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4200</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>-5600</v>
       </c>
       <c r="AJ101" s="3">
         <v>-5600</v>
       </c>
+      <c r="AK101" s="3">
+        <v>-5600</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-50200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>38600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-24100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>31300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>137400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>21800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>9500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-117600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-57900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>45400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>25200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>19200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>MEI</t>
   </si>
@@ -656,482 +656,495 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45598</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45500</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45409</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45318</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44590</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44044</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43953</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43862</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43764</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43673</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43582</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43491</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43400</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43309</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43218</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43127</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43036</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>257100</v>
+      </c>
+      <c r="E8" s="3">
         <v>239900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>292600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>258500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>277300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>259500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>288000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>289700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>301200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>280100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>315900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>282400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>288700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>291600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>295500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>287800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>301000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>295300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>190900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>210600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>285900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>257200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>270200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>266000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>246900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>264000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>223400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>249000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>228000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>230100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>201200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>219800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>195600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>236800</v>
+      </c>
+      <c r="E9" s="3">
         <v>198600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>234600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>213600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>241000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>222400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>235500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>235100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>237500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>215200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>241800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>220600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>233700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>221300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>226300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>216100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>225600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>222300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>217300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>143900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>151400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>206600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>188600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>194400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>195400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>179600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>190600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>163300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>187100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>167900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>167300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>145600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>164500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>142200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E10" s="3">
         <v>41300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>36300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>52500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>54600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>63700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>61800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>55000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>70300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>69200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>75400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>73000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>83500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>47000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>59200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>79300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>68600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>75800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>70600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>67300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>73400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>60100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>61900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>60100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>62800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>55600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>55300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>53400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,13 +1182,14 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>41800</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1183,11 +1197,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>49100</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1195,11 +1209,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>35000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1276,8 +1290,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1383,70 +1400,73 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>50300</v>
-      </c>
       <c r="H14" s="3">
+        <v>50200</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>57100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-4100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-2100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>500</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1457,41 +1477,44 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>4200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2600</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1499,25 +1522,25 @@
         <v>5800</v>
       </c>
       <c r="E15" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="F15" s="3">
         <v>5900</v>
       </c>
       <c r="G15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H15" s="3">
         <v>6000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4700</v>
       </c>
       <c r="L15" s="3">
         <v>4700</v>
@@ -1532,7 +1555,7 @@
         <v>4700</v>
       </c>
       <c r="P15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="Q15" s="3">
         <v>4800</v>
@@ -1547,49 +1570,49 @@
         <v>4800</v>
       </c>
       <c r="U15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="V15" s="3">
         <v>5000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>4700</v>
       </c>
       <c r="W15" s="3">
         <v>4700</v>
       </c>
       <c r="X15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Y15" s="3">
         <v>4800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>1900</v>
       </c>
       <c r="AE15" s="3">
         <v>1900</v>
       </c>
       <c r="AF15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AG15" s="3">
         <v>2000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>600</v>
-      </c>
-      <c r="AI15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>8</v>
@@ -1597,8 +1620,11 @@
       <c r="AK15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1659,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>278700</v>
+      </c>
+      <c r="E17" s="3">
         <v>242100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>283100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>265400</v>
       </c>
-      <c r="G17" s="3">
-        <v>286100</v>
-      </c>
       <c r="H17" s="3">
+        <v>286600</v>
+      </c>
+      <c r="I17" s="3">
         <v>262400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>282200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>285200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>284100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>252500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>282900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>256500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>271200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>258700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>260200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>251800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>265100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>257200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>252500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>174200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>174300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>244400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>226500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>231600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>233000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>220900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>244900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>194700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>221400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>192400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>200400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>175800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>193800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>166500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-8800</v>
-      </c>
       <c r="H18" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>35900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>38100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>48300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>36300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>41500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>38600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>33000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>19100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>28700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>27600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>35600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>29700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>25400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>26000</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>29100</v>
       </c>
       <c r="AK18" s="3">
         <v>29100</v>
       </c>
+      <c r="AL18" s="3">
+        <v>29100</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,296 +1919,303 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>900</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="T20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="W20" s="3">
+        <v>500</v>
+      </c>
+      <c r="X20" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AG20" s="3">
         <v>3500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>500</v>
-      </c>
-      <c r="W20" s="3">
-        <v>5900</v>
-      </c>
-      <c r="X20" s="3">
-        <v>4900</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-600</v>
       </c>
       <c r="AH20" s="3">
         <v>-600</v>
       </c>
       <c r="AI20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E21" s="3">
         <v>3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I21" s="3">
         <v>700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>36100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>46100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>48500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>50800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>51300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>60200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>29300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>54500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>58700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>43600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>50300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>27600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>36600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>46200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>36400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>30400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>34600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>36200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5000</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1100</v>
       </c>
       <c r="R22" s="3">
         <v>1100</v>
       </c>
       <c r="S22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
@@ -2183,8 +2223,8 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2207,222 +2247,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-63100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-55500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>34800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>46200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>15600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>40100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>29000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>35600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>30100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>27700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>17600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>30800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>39100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>29100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>24800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>30300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-5100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2528,222 +2577,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-57300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-55300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>29400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>38600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>20700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>41200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>23800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>28300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>23700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>33700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>32500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>24200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>23700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-57300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-55300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>29400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>38600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>20700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>41200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>23800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>28300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>33700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>32500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>24200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>23700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2849,8 +2907,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2908,8 +2969,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2923,26 +2984,26 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>4800</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>3100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-56800</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2956,8 +3017,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3127,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,222 +3237,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>700</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="M32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="T32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U32" s="3">
+        <v>300</v>
+      </c>
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="W32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>500</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>600</v>
       </c>
       <c r="AH32" s="3">
         <v>600</v>
       </c>
       <c r="AI32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-57300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-55300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>29400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>38600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>20700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>41200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>23800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>28300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>30700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>36800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>24200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>23700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3567,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-57300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-55300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>29400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>38600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>20700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>41200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>23800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>28300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>30700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>36800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>24200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>23700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45598</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45500</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45409</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45318</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44590</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44044</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43953</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43862</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43764</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43673</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43582</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43491</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43400</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43309</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43218</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43127</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43036</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +3834,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,115 +3874,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E41" s="3">
         <v>103800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>97000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>111300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>161500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>157000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>164700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>152400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>172000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>153100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>177200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>207900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>233200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>218700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>242300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>211000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>217300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>79900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>95600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>73800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>83200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>73700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>110900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>228500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>246100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>304000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>258600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>297900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>294000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>268800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>249600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3919,14 +4009,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4002,436 +4092,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>245100</v>
+      </c>
+      <c r="E43" s="3">
         <v>224200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>260800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>252700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>266600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>283900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>309000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>314200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>327200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>303000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>321000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>289700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>281600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>299400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>295000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>290000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>294000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>284000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>301100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>246600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>201400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>237600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>217300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>246500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>233600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>226200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>240200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>191000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>205000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>202000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>216000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>165100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>165900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>153800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>194100</v>
+      </c>
+      <c r="E44" s="3">
         <v>218800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>228200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>219900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>186200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>204000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>183900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>175600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>159700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>175400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>172500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>173900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>158500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>167000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>142400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>124200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>124000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>120700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>124000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>131000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>126100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>133800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>122000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>116700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>124000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>118300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>88500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>84100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>83600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>78400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>64800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>57900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>62000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>2700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>18200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>16400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>18700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>22500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>21700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>15900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>14800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>15700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>15900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>19100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>14500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>559900</v>
+      </c>
+      <c r="E46" s="3">
         <v>572200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>612900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>611800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>637700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>629800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>636500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>657500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>664400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>671000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>658400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>639100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>629000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>640400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>643100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>660900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>674000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>645000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>682300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>598000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>565600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>463900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>465400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>461300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>453500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>446400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>491100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>523900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>550000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>605300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>568900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>546900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>530300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>499100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4459,8 +4564,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4537,222 +4642,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E48" s="3">
         <v>233500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>244400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>239200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>238800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>258400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>251500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>254700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>248700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>230100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>213800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>212800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>217000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>218600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>228400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>235200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>226300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>228700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>226700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>230700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>225400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>226300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>226700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>222500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>191900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>189100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>187900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>165300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>162200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>153700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>126900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>117400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>90600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>87700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>411100</v>
+      </c>
+      <c r="E49" s="3">
         <v>403100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>416400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>422800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>426600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>484700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>485400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>553800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>558600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>425800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>427700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>435300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>440700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>447300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>454100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>459300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>465000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>468500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>470300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>475400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>476400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>484200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>489400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>493400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>498200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>504400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>509000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>117000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>120200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>125200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>123400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>36100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +4972,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,115 +5082,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E52" s="3">
         <v>21500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>34700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>34000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>37700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>101600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>94400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>102700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>102400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>105000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>105100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>103600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>101700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>102300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>110000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>114100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>103200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>107900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>101200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>91700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>88100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>86300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>82500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>86600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>83500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>75600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>79100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>83000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>74900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>71400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,115 +5302,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1305800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1304600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1375100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1377900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1403500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1491500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1484900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1574100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1579100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1428500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1394300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1389900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1389100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1411300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1430700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1459000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1467000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1444500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1489300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1418200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1370600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1282300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1282700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1268900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1231700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1226200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1270500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>892800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>915900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>959800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>898300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>783400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>704000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>667000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5454,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,147 +5494,151 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E57" s="3">
         <v>107700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>129800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>161100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>132400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>146000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>131900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>138700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>113100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>116400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>108500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>115900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>118600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>110800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>122900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>117800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>112400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>83200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>73800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>88800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>97100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>90700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>91900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>88600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>105600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>79000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>89500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>87900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>99300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>81200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>75300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>67700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E58" s="3">
         <v>7700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
-      </c>
-      <c r="M58" s="3">
-        <v>13000</v>
       </c>
       <c r="N58" s="3">
         <v>13000</v>
@@ -5513,64 +5647,64 @@
         <v>13000</v>
       </c>
       <c r="P58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>13200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3800</v>
-      </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>8</v>
@@ -5578,436 +5712,451 @@
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E59" s="3">
         <v>15100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>75500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>78500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>84900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>76000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>71000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>61400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>54700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>59700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>72000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>74700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>73300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>72600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>71300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>53900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>63100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>59500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>50700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>41500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>49100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>43500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>233200</v>
+      </c>
+      <c r="E60" s="3">
         <v>201400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>222600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>260800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>231400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>229900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>218300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>208400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>228000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>190900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>213000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>195800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>188600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>203700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>207800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>204100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>222700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>209200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>198700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>160000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>143800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>163600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>184300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>180800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>180900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>176400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>192200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>136800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>157000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>150300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>152300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>126500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>124400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>111200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>341300</v>
+      </c>
+      <c r="E61" s="3">
         <v>352200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>366700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>319100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>353400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>355200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>351000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>359300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>325400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>191000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>194200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>197500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>202400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>208400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>220600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>225200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>229200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>332300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>334400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>336800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>241900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>259900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>267700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>276900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>287700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>342300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>49200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>53400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>116000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>105500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>47600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>37000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E62" s="3">
         <v>17000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>94200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>91500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>88500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>89200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>88800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>95000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>100000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>101100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>108500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>106900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>110000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>106600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>103900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>105900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>106100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>84200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>88000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>92700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>74600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>75500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>86300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>33700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>19900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>10900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6262,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6220,8 +6372,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,115 +6482,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>612500</v>
+      </c>
+      <c r="E66" s="3">
         <v>600300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>636800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>633500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>637500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>656500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>640000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>641800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>626200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>485900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>495500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>478500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>475300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>494900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>511200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>524700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>549000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>546900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>637900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>604400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>587200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>509400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>550100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>554600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>542000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>552100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>627200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>260600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>285900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>352600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>291500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>194000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>162900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>159100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +6634,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +6742,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +6852,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +6962,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,115 +7072,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>524200</v>
+      </c>
+      <c r="E72" s="3">
         <v>558300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>580600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>587100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>612300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>677600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>697000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>764800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>772700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>778200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>771200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>768100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>763900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>752900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>749800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>761900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>746000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>726600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>698900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>664600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>651900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>625600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>588500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>568900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>545200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>526700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>500000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>490000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>472000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>439200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>467400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>446600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>427000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>407200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>387200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7292,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7402,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,115 +7512,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>693300</v>
+      </c>
+      <c r="E76" s="3">
         <v>704300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>738300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>744400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>766000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>835000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>844900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>931400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>941800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>942600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>898800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>911400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>913800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>916400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>919500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>934300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>918000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>897600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>851400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>813800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>783400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>772900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>732600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>714300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>689700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>674100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>643300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>632200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>630000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>607200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>606800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>589400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>541100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>507900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>492800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +7732,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45598</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45500</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45409</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45318</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44590</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44044</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43953</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43862</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43764</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43673</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43582</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43491</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43400</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43309</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43218</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43127</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43036</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-57300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-55300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>29400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>38600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>20700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>41200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>23800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>28300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>30700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>36800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>24200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>23700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,115 +7999,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E83" s="3">
         <v>8800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>12300</v>
       </c>
       <c r="X83" s="3">
         <v>12300</v>
       </c>
       <c r="Y83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>11900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6700</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>5900</v>
       </c>
       <c r="AK83" s="3">
         <v>5900</v>
       </c>
+      <c r="AL83" s="3">
+        <v>5900</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8217,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8327,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +8437,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +8547,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +8657,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E89" s="3">
         <v>28100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-48000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>55700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>42000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>36000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>87100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>58000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>48700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>19100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>37700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>28100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>16200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>20000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>30700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>41900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>21600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>23600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>38500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>43000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +8809,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9027,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9137,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>21500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-125800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15400</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-4800</v>
       </c>
       <c r="T94" s="3">
         <v>-4800</v>
       </c>
       <c r="U94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-431300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-29900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,100 +9289,101 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E96" s="3">
         <v>5300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5100</v>
-      </c>
-      <c r="G96" s="3">
-        <v>4900</v>
       </c>
       <c r="H96" s="3">
         <v>4900</v>
       </c>
       <c r="I96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J96" s="3">
         <v>4800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-5000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-4900</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-5000</v>
       </c>
       <c r="O96" s="3">
         <v>-5000</v>
       </c>
       <c r="P96" s="3">
-        <v>-5100</v>
+        <v>-5000</v>
       </c>
       <c r="Q96" s="3">
         <v>-5100</v>
       </c>
       <c r="R96" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="S96" s="3">
         <v>-5200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-4200</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-4100</v>
       </c>
       <c r="U96" s="3">
         <v>-4100</v>
       </c>
       <c r="V96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W96" s="3">
         <v>-5000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-4100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-4100</v>
       </c>
       <c r="Z96" s="3">
         <v>-4100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-4500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-4100</v>
       </c>
       <c r="AE96" s="3">
         <v>-4100</v>
       </c>
       <c r="AF96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-3400</v>
       </c>
       <c r="AH96" s="3">
         <v>-3400</v>
@@ -9158,13 +9392,16 @@
         <v>-3400</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +9507,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +9617,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,325 +9727,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>40100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>66800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-20800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-51400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-18300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-108600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-13000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>91400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-58800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>300500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-70300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>56900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-18100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E101" s="3">
         <v>5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>15900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4200</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>-5600</v>
       </c>
       <c r="AK101" s="3">
         <v>-5600</v>
       </c>
+      <c r="AL101" s="3">
+        <v>-5600</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-50200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>38600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>35100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-30700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-23600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>31300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>137400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>21800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-117600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-57900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>45400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>19200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>MEI</t>
   </si>
@@ -656,508 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F7" s="2">
         <v>45871</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45780</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45689</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45598</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45500</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45409</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45318</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45227</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45136</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45045</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44954</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44863</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44772</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44590</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44499</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44317</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44226</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44044</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43953</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43862</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43764</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43673</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43582</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43491</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43400</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43309</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43218</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43127</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43036</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42945</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42854</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42763</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>233700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>246900</v>
+      </c>
+      <c r="F8" s="3">
         <v>240500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>257100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>239900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>292600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>258500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>277300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>259500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>288000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>289700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>301200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>280100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>315900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>282400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>288700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>291600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>295500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>287800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>301000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>295300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>300800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>190900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>210600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>285900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>257200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>270200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>266000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>246900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>264000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>223400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>249000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>228000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>230100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>201200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>219800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>195600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>199100</v>
+      </c>
+      <c r="F9" s="3">
         <v>197000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>236800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>198600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>234600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>213600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>241000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>222400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>235500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>235100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>237500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>215200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>241800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>220600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>233700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>221300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>226300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>216100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>225600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>222300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>217300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>143900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>151400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>206600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>188600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>194400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>195400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>179600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>190600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>163300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>187100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>167900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>167300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>145600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>164500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>142200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>47800</v>
+      </c>
+      <c r="F10" s="3">
         <v>43500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>20300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>41300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>58000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>44900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>36300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>37100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>52500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>54600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>63700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>64900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>74100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>61800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>55000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>70300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>69200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>71700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>75400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>73000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>83500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>47000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>59200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>79300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>68600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>75800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>70600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>67300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>73400</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>60100</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>61900</v>
       </c>
       <c r="AH10" s="3">
         <v>60100</v>
       </c>
       <c r="AI10" s="3">
+        <v>61900</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>60100</v>
+      </c>
+      <c r="AK10" s="3">
         <v>62800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>55600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>55300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>53400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1197,46 +1222,48 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
-        <v>41800</v>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>41800</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
-        <v>49100</v>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
+      <c r="K12" s="3">
+        <v>49100</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
-        <v>35000</v>
+      <c r="M12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
+      <c r="O12" s="3">
+        <v>35000</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
@@ -1310,8 +1337,14 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1423,8 +1456,14 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,70 +1471,70 @@
         <v>400</v>
       </c>
       <c r="E14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>400</v>
+      </c>
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>50200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>57100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>4400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-2600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-2100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-2300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>500</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1503,41 +1542,47 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>3800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>10900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>2600</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1551,28 +1596,28 @@
         <v>5800</v>
       </c>
       <c r="G15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I15" s="3">
         <v>5900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>5900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>6000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>6100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>6200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>5700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>4700</v>
       </c>
       <c r="O15" s="3">
         <v>4700</v>
@@ -1584,10 +1629,10 @@
         <v>4700</v>
       </c>
       <c r="R15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="S15" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="T15" s="3">
         <v>4800</v>
@@ -1599,16 +1644,16 @@
         <v>4800</v>
       </c>
       <c r="W15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="X15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>5000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>4700</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>4700</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>4800</v>
       </c>
       <c r="AA15" s="3">
         <v>4700</v>
@@ -1617,40 +1662,46 @@
         <v>4800</v>
       </c>
       <c r="AC15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE15" s="3">
         <v>5000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>5500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>3700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>1900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>1900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>2000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>600</v>
-      </c>
-      <c r="AK15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1687,234 +1738,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>239400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>242900</v>
+      </c>
+      <c r="F17" s="3">
         <v>238500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>278700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>242100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>283100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>265400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>286600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>262400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>282200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>285200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>284100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>252500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>282900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>256500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>271200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>258700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>260200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>251800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>265100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>257200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>252500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>174200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>174300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>244400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>226500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>231600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>233000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>220900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>244900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>194700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>221400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>192400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>200400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>175800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>193800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>166500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-21600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-9300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>17100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>27600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>33000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>25900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>17500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>32900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>35300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>36000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>35900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>38100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>48300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>16700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>36300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>41500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>30700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>38600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>33000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>26000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>19100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>28700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>27600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>35600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>29700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>25400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>26000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>29100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1954,326 +2019,340 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>7800</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-3800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>5900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>3200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>3500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>1900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>1200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F21" s="3">
         <v>6600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-18500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>10900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>18300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>36100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>46100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>38200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>30800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>47900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>47400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>48500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>50800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>51300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>60200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>29300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>54500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>58700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>43600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>50300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>42800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>39900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>27600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>36600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>38900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>46200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>36400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>30400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>34600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>36200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F22" s="3">
         <v>5900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>5400</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3">
-        <v>5000</v>
-      </c>
       <c r="I22" s="3">
-        <v>4100</v>
+        <v>6500</v>
       </c>
       <c r="J22" s="3">
         <v>5000</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>2100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>2400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>2700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>2900</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
@@ -2293,234 +2372,252 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-30400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-13100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-63100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-10500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-55500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>7800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>33400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>25900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>17200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>33500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>33000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>34800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>36600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>36500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>46200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>15600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>40100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>44000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>29000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>35600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>30100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>27700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>17600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>28200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>30800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>39100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>29100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>24800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>27900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>30300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>5200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>5500</v>
-      </c>
-      <c r="T24" s="3">
-        <v>5700</v>
       </c>
       <c r="U24" s="3">
         <v>5500</v>
       </c>
       <c r="V24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="W24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="X24" s="3">
         <v>4600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>7600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>10000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>5200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>7300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>7500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>3000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>4500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>6600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>4300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>4700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>6600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2632,234 +2729,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-28300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-14400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-18300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-57300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-11600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-55300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>19900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>27600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>21500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>16200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>29400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>27500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>29100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>31100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>31900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>38600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>20700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>30100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>41200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>23800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>28300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>22600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>25900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>14600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>23700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>33700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>32500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>20500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>23200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>23700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-28300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-14400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-18300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-57300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-55300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>19900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>27600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>21500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>16200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>29400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>27500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>29100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>31100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>31900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>38600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>20700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>30100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>41200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>23800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>28300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>22600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>25900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>14600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>23700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>33700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>32500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>20500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>23200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>23700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2971,8 +3086,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3036,11 +3157,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3051,29 +3172,29 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>4800</v>
       </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>3100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-56800</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3084,8 +3205,14 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3197,8 +3324,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3310,234 +3443,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-28300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-14400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-18300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-57300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-55300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>19900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>27600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>21500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>16200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>29400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>27500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>29100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>31100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>31900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>38600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>20700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>30100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>41200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>23800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>28300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>22600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>30700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>14600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>23700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>36800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>20500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>23200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>23700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3649,239 +3800,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-28300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-14400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-18300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-57300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-55300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>19900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>27600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>21500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>16200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>29400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>27500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>29100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>31100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>31900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>38600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>20700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>30100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>41200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>23800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>28300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>22600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>30700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>14600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>23700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>36800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>20500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>23200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>23700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F38" s="2">
         <v>45871</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45780</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45689</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45598</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45500</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45409</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45318</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45227</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45136</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45045</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44954</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44863</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44772</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44590</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44499</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44317</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44226</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44044</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43953</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43862</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43764</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43673</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43582</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43491</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43400</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43309</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43218</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43127</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43036</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42945</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42854</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42763</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3921,8 +4090,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3962,121 +4133,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>118500</v>
+      </c>
+      <c r="F41" s="3">
         <v>121100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>103600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>103800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>97000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>111300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>161500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>122900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>122500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>147900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>157000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>164700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>129600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>152400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>172000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>153100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>177200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>207900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>233200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>218700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>242300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>211000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>217300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>79900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>95600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>73800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>83200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>73700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>110900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>228500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>246100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>304000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>258600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>297900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>294000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>268800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>249600</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4105,17 +4284,17 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1600</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4188,460 +4367,490 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>232100</v>
+      </c>
+      <c r="F43" s="3">
         <v>221300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>245100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>224200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>260800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>252700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>266600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>283900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>309000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>314200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>327200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>303000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>321000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>289700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>281600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>299400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>295000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>290000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>294000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>284000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>301100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>246600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>201400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>237600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>217300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>246500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>233600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>226200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>240200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>191000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>205000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>202000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>216000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>165100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>165900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>153800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>209800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>190200</v>
+      </c>
+      <c r="F44" s="3">
         <v>190900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>194100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>218800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>228200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>219900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>186200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>204000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>183900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>175600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>159700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>175400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>172500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>173900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>158500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>167000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>149000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>142400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>124200</v>
-      </c>
-      <c r="V44" s="3">
-        <v>124000</v>
-      </c>
-      <c r="W44" s="3">
-        <v>120700</v>
       </c>
       <c r="X44" s="3">
         <v>124000</v>
       </c>
       <c r="Y44" s="3">
+        <v>120700</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>124000</v>
+      </c>
+      <c r="AA44" s="3">
         <v>131000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>126100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>133800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>122000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>116700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>124000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>118300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>88500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>84100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>83600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>78400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>64800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>57900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>62000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>27900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>35300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>23100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>16900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>20900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>21900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>20600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>22600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>18300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>18200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>16400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>15900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>20300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>18700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>19000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>20000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>22500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>21700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>15900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>14800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>15700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>19100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>12500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>14500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>585300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>555300</v>
+      </c>
+      <c r="F46" s="3">
         <v>549200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>559900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>572200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>612900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>611800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>637700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>629800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>636500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>657500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>664400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>671000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>658400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>639100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>629000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>640400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>643100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>660900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>674000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>645000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>682300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>598000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>565600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>463900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>465400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>461300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>453500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>446400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>491100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>523900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>550000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>605300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>568900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>546900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>530300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>499100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4675,11 +4884,11 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4753,234 +4962,252 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>246200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>246100</v>
+      </c>
+      <c r="F48" s="3">
         <v>246600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>245300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>233500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>244400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>239200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>238800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>258400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>251500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>254700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>248700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>230100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>213800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>212800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>217000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>218600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>228400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>235200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>226300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>228700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>226700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>230700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>225400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>226300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>226700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>222500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>191900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>189100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>187900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>165300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>162200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>153700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>126900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>117400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>90600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>87700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>401100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>402000</v>
+      </c>
+      <c r="F49" s="3">
         <v>408800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>411100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>403100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>416400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>422800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>426600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>484700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>485400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>553800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>558600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>425800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>427700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>435300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>440700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>447300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>454100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>459300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>465000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>468500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>470300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>475400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>476400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>484200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>489400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>493400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>498200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>504400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>509000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>117000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>120200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>125200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>123400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>36100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>8200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>8800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5092,8 +5319,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5205,121 +5438,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F52" s="3">
         <v>20200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>20000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>21500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>21900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>22000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>21600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>34700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>34000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>35500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>37700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>101600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>94400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>102700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>102400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>105000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>105100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>103600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>101700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>102300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>110000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>114100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>103200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>107900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>101200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>91700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>88100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>86300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>82500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>86600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>83500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>75600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>79100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>83000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>74900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>71400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5431,121 +5676,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1306300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1287400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1291300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1305800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1304600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1375100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1377900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1403500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1491500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1484900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1574100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1579100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1428500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1394300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1389900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1389100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1411300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1430700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1459000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1467000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1444500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1489300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1418200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1370600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1282300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1282700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1268900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1231700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1226200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1270500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>892800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>915900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>959800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>898300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>783400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>704000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>667000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5585,8 +5842,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5626,183 +5885,191 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>124200</v>
+      </c>
+      <c r="F57" s="3">
         <v>123500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>125900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>107700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>129800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>161100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>132400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>146000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>133500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>131900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>138700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>113100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>124500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>116400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>108500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>115900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>118600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>110800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>122900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>117800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>112400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>83200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>73800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>88800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>97100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>90700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>91900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>88600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>105600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>79000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>89500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>87900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>99300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>81200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>75300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>67700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F58" s="3">
         <v>7600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>7600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>7700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>9600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>10100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>10000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
-      </c>
-      <c r="O58" s="3">
-        <v>13000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>13000</v>
       </c>
       <c r="Q58" s="3">
         <v>13000</v>
       </c>
       <c r="R58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="S58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="T58" s="3">
         <v>13200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>14700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>14800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>14900</v>
-      </c>
-      <c r="V58" s="3">
-        <v>15400</v>
-      </c>
-      <c r="W58" s="3">
-        <v>15300</v>
       </c>
       <c r="X58" s="3">
         <v>15400</v>
@@ -5811,501 +6078,531 @@
         <v>15300</v>
       </c>
       <c r="Z58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AB58" s="3">
         <v>15100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>15200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>15400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>15700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>15200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>15300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>4400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>2900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>3800</v>
-      </c>
-      <c r="AK58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F59" s="3">
         <v>17000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>17500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>15100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>8400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>9800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>7900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>7600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>77300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>75500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>66400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>67100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>74600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>74500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>78500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>84900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>76000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>71000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>61400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>54700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>59700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>72000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>74700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>73300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>72600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>71300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>53900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>63100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>59500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>50700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>41500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>49100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>43500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>242800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>217600</v>
+      </c>
+      <c r="F60" s="3">
         <v>219600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>233200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>201400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>222600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>260800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>231400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>229900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>218300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>208400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>228000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>190900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>213000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>195800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>188600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>203700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>207800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>204100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>222700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>209200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>198700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>160000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>143800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>163600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>184300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>180800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>180900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>176400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>192200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>136800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>157000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>150300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>152300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>126500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>124400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>111200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>359600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>352000</v>
+      </c>
+      <c r="F61" s="3">
         <v>345000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>341300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>352200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>366700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>319100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>353400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>355200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>351000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>359300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>325400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>200800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>191000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>194200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>197500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>202400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>208400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>220600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>225200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>229200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>332300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>334400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>336800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>241900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>259900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>267700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>276900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>287700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>342300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>49200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>53400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>116000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>105500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>47600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>27000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>37000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F62" s="3">
         <v>11700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>11200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>17000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>16600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>25700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>24000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>25000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>24700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>32700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>31000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>94200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>91500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>88500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>89200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>88800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>95000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>100000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>101100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>108500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>106900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>110000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>106600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>103900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>105900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>106100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>84200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>88000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>92700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>74600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>75500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>86300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>33700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>19900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>11500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>10900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6417,8 +6714,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6530,8 +6833,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6643,121 +6952,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>631300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>608100</v>
+      </c>
+      <c r="F66" s="3">
         <v>603200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>612500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>600300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>636800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>633500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>637500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>656500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>640000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>641800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>626200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>485900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>495500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>478500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>475300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>494900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>511200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>524700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>549000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>546900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>637900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>604400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>587200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>509400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>550100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>554600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>542000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>552100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>627200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>260600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>285900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>352600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>291500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>194000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>162900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>159100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6797,8 +7118,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6910,8 +7233,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7023,8 +7352,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7136,8 +7471,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7249,121 +7590,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>481000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>498900</v>
+      </c>
+      <c r="F72" s="3">
         <v>511000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>524200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>558300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>580600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>587100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>612300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>677600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>697000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>764800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>772700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>778200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>771200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>768100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>763900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>752900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>749800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>761900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>746000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>726600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>698900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>664600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>651900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>625600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>588500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>568900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>545200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>526700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>500000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>490000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>472000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>439200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>467400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>446600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>427000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>407200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>387200</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7475,8 +7828,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7588,8 +7947,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7701,121 +8066,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>675000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>679300</v>
+      </c>
+      <c r="F76" s="3">
         <v>688100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>693300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>704300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>738300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>744400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>766000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>835000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>844900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>931400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>941800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>942600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>898800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>911400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>913800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>916400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>919500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>934300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>918000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>897600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>851400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>813800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>783400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>772900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>732600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>714300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>689700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>674100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>643300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>632200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>630000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>607200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>606800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>589400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>541100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>507900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>492800</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7927,239 +8304,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F80" s="2">
         <v>45871</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45780</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45689</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45598</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45500</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45409</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45318</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45227</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45136</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45045</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44954</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44863</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44772</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44590</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44499</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44317</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44226</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44044</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43953</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43862</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43764</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43673</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43582</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43491</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43400</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43309</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43218</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43127</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43036</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42945</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42854</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42763</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-28300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-14400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-18300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-57300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-55300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>19900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>27600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>21500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>16200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>29400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>27500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>29100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>31100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>31900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>38600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>20700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>30100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>41200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>23800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>28300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>22600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>30700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>14600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>23700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>36800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>20500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>23200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>23700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8199,121 +8594,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F83" s="3">
         <v>8200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>8800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>8200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>8300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>8000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>7500</v>
       </c>
       <c r="L83" s="3">
         <v>7600</v>
       </c>
       <c r="M83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="N83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O83" s="3">
         <v>8300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>12300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>12200</v>
       </c>
       <c r="P83" s="3">
         <v>12300</v>
       </c>
       <c r="Q83" s="3">
+        <v>12200</v>
+      </c>
+      <c r="R83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="S83" s="3">
         <v>13000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>13700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>13300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>12600</v>
       </c>
       <c r="U83" s="3">
         <v>13300</v>
       </c>
       <c r="V83" s="3">
+        <v>12600</v>
+      </c>
+      <c r="W83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="X83" s="3">
         <v>13500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>12600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>12100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>12300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>12300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>11900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>11800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>12700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>12200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>10000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>8400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>8100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>7100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>5600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>6700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>5900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8425,8 +8828,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8538,8 +8947,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8651,8 +9066,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8764,8 +9185,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8877,121 +9304,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F89" s="3">
         <v>25100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>35400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>28100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-48000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>10900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>24900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>28800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>49000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>55700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>15400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>12700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>42000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>20100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>27000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>9700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>36000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>87100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>40300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>16400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>58000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>14800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>48700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>19100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>37700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>28100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>16200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>20000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>30700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>41900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>21600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>23600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>38500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>43000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9031,121 +9470,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-10400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-13600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-9100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-16600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-13800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-11200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12800</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-9600</v>
       </c>
       <c r="Q91" s="3">
         <v>-8400</v>
       </c>
       <c r="R91" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="T91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-5400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-15900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-4900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9257,8 +9704,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9370,121 +9823,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-13600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>21500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-16700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-13800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-125800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-8400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-8300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-5300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-15400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-4800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-431300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-18200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-29900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9524,121 +9989,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F96" s="3">
         <v>2800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>5100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>5300</v>
-      </c>
-      <c r="G96" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H96" s="3">
-        <v>5100</v>
       </c>
       <c r="I96" s="3">
         <v>4900</v>
       </c>
       <c r="J96" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K96" s="3">
         <v>4900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M96" s="3">
         <v>4800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>5300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>4900</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-4900</v>
       </c>
       <c r="P96" s="3">
         <v>-5000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="R96" s="3">
         <v>-5000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-5100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-5100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-5200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-4200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-4100</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-5000</v>
       </c>
       <c r="Y96" s="3">
         <v>-4100</v>
       </c>
       <c r="Z96" s="3">
-        <v>-4000</v>
+        <v>-5000</v>
       </c>
       <c r="AA96" s="3">
         <v>-4100</v>
       </c>
       <c r="AB96" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-4100</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-3600</v>
       </c>
       <c r="AD96" s="3">
         <v>-4100</v>
       </c>
       <c r="AE96" s="3">
-        <v>-4500</v>
+        <v>-3600</v>
       </c>
       <c r="AF96" s="3">
         <v>-4100</v>
       </c>
       <c r="AG96" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-3400</v>
       </c>
       <c r="AK96" s="3">
         <v>-3400</v>
       </c>
       <c r="AL96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9750,8 +10223,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9863,8 +10342,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9976,343 +10461,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-42300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-8500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>40100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-48200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-3900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-16900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-10600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>12500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>66800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-14900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-27900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-10800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-34100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-51400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-18300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-15100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-108600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-6200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>91400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-58800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>300500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-70300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>6400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>56900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-14500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-18100</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-3900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>5200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>7100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>7100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-5400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-3900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>1900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>16100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>15900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>4200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F102" s="3">
         <v>17500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>6800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-14300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-50200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>38600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-25400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-9100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-7700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>35100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-22800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>18900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-24100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-30700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-25300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>14500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-23600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>31300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>137400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-15700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>21800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>9500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-117600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-57900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>45400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-39300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>3900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>25200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>19200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MEI_QTR_FIN.xlsx
@@ -6021,7 +6021,7 @@
         <v>7600</v>
       </c>
       <c r="G58" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="H58" s="3">
         <v>7700</v>
@@ -6378,7 +6378,7 @@
         <v>345000</v>
       </c>
       <c r="G61" s="3">
-        <v>341300</v>
+        <v>341600</v>
       </c>
       <c r="H61" s="3">
         <v>352200</v>
@@ -6497,7 +6497,7 @@
         <v>11700</v>
       </c>
       <c r="G62" s="3">
-        <v>11200</v>
+        <v>10900</v>
       </c>
       <c r="H62" s="3">
         <v>17000</v>
